--- a/src/templates/arnes.xlsx
+++ b/src/templates/arnes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tesisSanCristobal\forms\BackendForm\BackendForm\src\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AE523FD-BC00-4707-BDCE-6C84B1D8D3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD9E098-42B5-4D30-8495-671D9858635E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ANVERSO" sheetId="3" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="167">
   <si>
     <t>ÁREA/SECCIÓN:</t>
   </si>
@@ -82,9 +82,6 @@
   </si>
   <si>
     <t>Operatividad</t>
-  </si>
-  <si>
-    <t>MARCA:…..............................................................................</t>
   </si>
   <si>
     <t>Ítems de Evaluación</t>
@@ -98,9 +95,6 @@
   <si>
     <t>LISTA DE CHEQUEO
 SISTEMAS DE PROTECCIÓN CONTRA CAÍDAS (SPCC)</t>
-  </si>
-  <si>
-    <t>COD. DEL CONECTOR:…...........................................................</t>
   </si>
   <si>
     <t>HEBILLAS</t>
@@ -237,9 +231,6 @@
   </si>
   <si>
     <t>4.7</t>
-  </si>
-  <si>
-    <t>COD. DEL ANCLAJE:…...........................................................</t>
   </si>
   <si>
     <t>Los ganchos o mordazas para vigas abren y cierran correctamente, sin trabarse ni presentar juego excesivo</t>
@@ -492,12 +483,6 @@
   </si>
   <si>
     <t>COD.:…….............</t>
-  </si>
-  <si>
-    <t>TIPO DE CONECTOR (H, I o J):…….............................................................................</t>
-  </si>
-  <si>
-    <t>TIPO DE ANCLAJE (K, L, M, N y O):…….............................................................................</t>
   </si>
   <si>
     <t>Está libre de manchas de pintura, grasa, productos químicos o humedad que deterioren el material</t>
@@ -716,22 +701,34 @@
     <t xml:space="preserve">  </t>
   </si>
   <si>
-    <t>COD. AUTORETRACTIL 1:</t>
-  </si>
-  <si>
-    <t>COD. AUTORETRACTIL 2:</t>
-  </si>
-  <si>
-    <t>TIPO DE ARNÉS (A, B o C):</t>
-  </si>
-  <si>
-    <t>MARCA:</t>
-  </si>
-  <si>
-    <t>COD. DEL ARNÉS:</t>
-  </si>
-  <si>
-    <t>TIPO AUTORETRACTIL (E, F o G):</t>
+    <t>TIPO DE ARNÉS (A, B o C)</t>
+  </si>
+  <si>
+    <t>MARCA</t>
+  </si>
+  <si>
+    <t>COD. DEL ARNÉS</t>
+  </si>
+  <si>
+    <t>TIPO AUTORETRACTIL (E, F o G)</t>
+  </si>
+  <si>
+    <t>COD. AUTORETRACTIL 1</t>
+  </si>
+  <si>
+    <t>COD. AUTORETRACTIL 2</t>
+  </si>
+  <si>
+    <t>TIPO DE CONECTOR (H, I o J)</t>
+  </si>
+  <si>
+    <t>COD. DEL CONECTOR</t>
+  </si>
+  <si>
+    <t>TIPO DE ANCLAJE (K, L, M, N y O)</t>
+  </si>
+  <si>
+    <t>COD. DEL ANCLAJE</t>
   </si>
 </sst>
 </file>
@@ -1211,6 +1208,174 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -1226,57 +1391,15 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1289,122 +1412,68 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1414,78 +1483,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5538,66 +5535,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="36.9" customHeight="1" thickBot="1">
-      <c r="A1" s="73"/>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="74" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="74"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="74"/>
-      <c r="Y1" s="39" t="s">
-        <v>154</v>
-      </c>
-      <c r="Z1" s="39"/>
+      <c r="A1" s="65"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="66" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="66"/>
+      <c r="T1" s="66"/>
+      <c r="U1" s="66"/>
+      <c r="V1" s="66"/>
+      <c r="W1" s="66"/>
+      <c r="X1" s="66"/>
+      <c r="Y1" s="95" t="s">
+        <v>149</v>
+      </c>
+      <c r="Z1" s="95"/>
     </row>
     <row r="2" spans="1:32" ht="27" customHeight="1" thickBot="1">
-      <c r="A2" s="73"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
-      <c r="N2" s="74"/>
-      <c r="O2" s="74"/>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="74"/>
-      <c r="S2" s="74"/>
-      <c r="T2" s="74"/>
-      <c r="U2" s="74"/>
-      <c r="V2" s="74"/>
-      <c r="W2" s="74"/>
-      <c r="X2" s="74"/>
-      <c r="Y2" s="40" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="66"/>
+      <c r="Q2" s="66"/>
+      <c r="R2" s="66"/>
+      <c r="S2" s="66"/>
+      <c r="T2" s="66"/>
+      <c r="U2" s="66"/>
+      <c r="V2" s="66"/>
+      <c r="W2" s="66"/>
+      <c r="X2" s="66"/>
+      <c r="Y2" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="Z2" s="40"/>
+      <c r="Z2" s="96"/>
     </row>
     <row r="3" spans="1:32" ht="8.4" customHeight="1">
       <c r="D3" s="6"/>
@@ -5628,147 +5625,147 @@
       <c r="A4" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
-      <c r="K4" s="76"/>
-      <c r="L4" s="70" t="s">
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="M4" s="70"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
       <c r="T4" s="11"/>
       <c r="U4" s="11"/>
       <c r="V4" s="17"/>
-      <c r="W4" s="70" t="s">
+      <c r="W4" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="X4" s="70"/>
-      <c r="Y4" s="70"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
       <c r="Z4" s="18"/>
     </row>
     <row r="5" spans="1:32" ht="6.6" customHeight="1">
-      <c r="A5" s="49"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="50"/>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
-      <c r="T5" s="50"/>
-      <c r="U5" s="50"/>
-      <c r="V5" s="50"/>
-      <c r="W5" s="50"/>
-      <c r="X5" s="50"/>
-      <c r="Y5" s="50"/>
-      <c r="Z5" s="50"/>
+      <c r="A5" s="98"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="98"/>
+      <c r="K5" s="99"/>
+      <c r="L5" s="99"/>
+      <c r="M5" s="99"/>
+      <c r="N5" s="99"/>
+      <c r="O5" s="99"/>
+      <c r="P5" s="99"/>
+      <c r="Q5" s="99"/>
+      <c r="R5" s="99"/>
+      <c r="S5" s="99"/>
+      <c r="T5" s="99"/>
+      <c r="U5" s="99"/>
+      <c r="V5" s="99"/>
+      <c r="W5" s="99"/>
+      <c r="X5" s="99"/>
+      <c r="Y5" s="99"/>
+      <c r="Z5" s="99"/>
     </row>
     <row r="6" spans="1:32" ht="27.75" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
+      <c r="P6" s="69"/>
+      <c r="Q6" s="69"/>
+      <c r="R6" s="69"/>
+      <c r="S6" s="69"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="69"/>
+      <c r="V6" s="69"/>
+      <c r="W6" s="69"/>
+      <c r="X6" s="69"/>
+      <c r="Y6" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="51"/>
-      <c r="S6" s="51"/>
-      <c r="T6" s="51"/>
-      <c r="U6" s="51"/>
-      <c r="V6" s="51"/>
-      <c r="W6" s="51"/>
-      <c r="X6" s="51"/>
-      <c r="Y6" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z6" s="79"/>
+      <c r="Z6" s="72"/>
     </row>
     <row r="7" spans="1:32" ht="33" customHeight="1">
-      <c r="A7" s="77" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" s="77"/>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="77"/>
-      <c r="G7" s="51" t="s">
+      <c r="A7" s="70" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="70"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="L7" s="51"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="51"/>
-      <c r="S7" s="51"/>
-      <c r="T7" s="51"/>
-      <c r="U7" s="51"/>
-      <c r="V7" s="51" t="s">
+      <c r="H7" s="69"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="L7" s="69"/>
+      <c r="M7" s="69"/>
+      <c r="N7" s="69"/>
+      <c r="O7" s="69"/>
+      <c r="P7" s="69"/>
+      <c r="Q7" s="69"/>
+      <c r="R7" s="69"/>
+      <c r="S7" s="69"/>
+      <c r="T7" s="69"/>
+      <c r="U7" s="69"/>
+      <c r="V7" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="W7" s="51"/>
-      <c r="X7" s="51"/>
-      <c r="Y7" s="80"/>
-      <c r="Z7" s="81"/>
+      <c r="W7" s="69"/>
+      <c r="X7" s="69"/>
+      <c r="Y7" s="73"/>
+      <c r="Z7" s="74"/>
     </row>
     <row r="8" spans="1:32" s="1" customFormat="1" ht="30.9" customHeight="1">
-      <c r="A8" s="84" t="s">
-        <v>164</v>
-      </c>
-      <c r="B8" s="84"/>
-      <c r="C8" s="84"/>
+      <c r="A8" s="80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B8" s="80"/>
+      <c r="C8" s="80"/>
       <c r="D8" s="12">
         <v>1</v>
       </c>
-      <c r="E8" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="F8" s="42"/>
+      <c r="E8" s="82" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" s="82"/>
       <c r="G8" s="8" t="s">
         <v>1</v>
       </c>
@@ -5778,24 +5775,24 @@
       <c r="I8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="52"/>
-      <c r="K8" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="L8" s="44"/>
-      <c r="M8" s="45"/>
+      <c r="J8" s="100"/>
+      <c r="K8" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="L8" s="38"/>
+      <c r="M8" s="39"/>
       <c r="N8" s="15">
         <v>1</v>
       </c>
-      <c r="O8" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="P8" s="47"/>
-      <c r="Q8" s="47"/>
-      <c r="R8" s="47"/>
-      <c r="S8" s="47"/>
-      <c r="T8" s="47"/>
-      <c r="U8" s="48"/>
+      <c r="O8" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="P8" s="87"/>
+      <c r="Q8" s="87"/>
+      <c r="R8" s="87"/>
+      <c r="S8" s="87"/>
+      <c r="T8" s="87"/>
+      <c r="U8" s="85"/>
       <c r="V8" s="8" t="s">
         <v>1</v>
       </c>
@@ -5805,1016 +5802,1016 @@
       <c r="X8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="Y8" s="82"/>
-      <c r="Z8" s="83"/>
+      <c r="Y8" s="75"/>
+      <c r="Z8" s="76"/>
     </row>
     <row r="9" spans="1:32" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A9" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="45"/>
+      <c r="A9" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" s="38"/>
+      <c r="C9" s="39"/>
       <c r="D9" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="53" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="53"/>
+      <c r="E9" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="60"/>
       <c r="G9" s="7"/>
       <c r="H9" s="3"/>
       <c r="I9" s="7"/>
-      <c r="J9" s="52"/>
-      <c r="K9" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="L9" s="44"/>
-      <c r="M9" s="45"/>
+      <c r="J9" s="100"/>
+      <c r="K9" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="L9" s="38"/>
+      <c r="M9" s="39"/>
       <c r="N9" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="54" t="s">
-        <v>146</v>
-      </c>
-      <c r="P9" s="55"/>
-      <c r="Q9" s="55"/>
-      <c r="R9" s="55"/>
-      <c r="S9" s="55"/>
-      <c r="T9" s="55"/>
-      <c r="U9" s="56"/>
+      <c r="O9" s="77" t="s">
+        <v>141</v>
+      </c>
+      <c r="P9" s="78"/>
+      <c r="Q9" s="78"/>
+      <c r="R9" s="78"/>
+      <c r="S9" s="78"/>
+      <c r="T9" s="78"/>
+      <c r="U9" s="79"/>
       <c r="V9" s="7"/>
       <c r="W9" s="3"/>
       <c r="X9" s="7"/>
-      <c r="Y9" s="57"/>
-      <c r="Z9" s="58"/>
+      <c r="Y9" s="46"/>
+      <c r="Z9" s="47"/>
     </row>
     <row r="10" spans="1:32" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A10" s="43" t="s">
-        <v>166</v>
-      </c>
-      <c r="B10" s="44"/>
-      <c r="C10" s="45"/>
+      <c r="A10" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="38"/>
+      <c r="C10" s="39"/>
       <c r="D10" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="53" t="s">
-        <v>131</v>
-      </c>
-      <c r="F10" s="53"/>
+      <c r="E10" s="60" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" s="60"/>
       <c r="G10" s="7"/>
       <c r="H10" s="3"/>
       <c r="I10" s="7"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="63" t="s">
-        <v>162</v>
-      </c>
-      <c r="L10" s="44"/>
-      <c r="M10" s="45"/>
+      <c r="J10" s="100"/>
+      <c r="K10" s="89" t="s">
+        <v>161</v>
+      </c>
+      <c r="L10" s="38"/>
+      <c r="M10" s="39"/>
       <c r="N10" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="O10" s="64" t="s">
-        <v>68</v>
-      </c>
-      <c r="P10" s="55"/>
-      <c r="Q10" s="55"/>
-      <c r="R10" s="55"/>
-      <c r="S10" s="55"/>
-      <c r="T10" s="55"/>
-      <c r="U10" s="56"/>
+      <c r="O10" s="88" t="s">
+        <v>65</v>
+      </c>
+      <c r="P10" s="78"/>
+      <c r="Q10" s="78"/>
+      <c r="R10" s="78"/>
+      <c r="S10" s="78"/>
+      <c r="T10" s="78"/>
+      <c r="U10" s="79"/>
       <c r="V10" s="21"/>
       <c r="W10" s="22"/>
       <c r="X10" s="21"/>
-      <c r="Y10" s="57"/>
-      <c r="Z10" s="58"/>
+      <c r="Y10" s="46"/>
+      <c r="Z10" s="47"/>
     </row>
     <row r="11" spans="1:32" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A11" s="59"/>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
+      <c r="A11" s="101"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="101"/>
       <c r="D11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="F11" s="53"/>
+      <c r="E11" s="60" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" s="60"/>
       <c r="G11" s="21"/>
       <c r="H11" s="22"/>
       <c r="I11" s="21"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="126" t="s">
-        <v>163</v>
-      </c>
-      <c r="L11" s="127"/>
-      <c r="M11" s="128"/>
+      <c r="J11" s="100"/>
+      <c r="K11" s="90" t="s">
+        <v>162</v>
+      </c>
+      <c r="L11" s="91"/>
+      <c r="M11" s="92"/>
       <c r="N11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="O11" s="54" t="s">
-        <v>69</v>
-      </c>
-      <c r="P11" s="55"/>
-      <c r="Q11" s="55"/>
-      <c r="R11" s="55"/>
-      <c r="S11" s="55"/>
-      <c r="T11" s="55"/>
-      <c r="U11" s="56"/>
+      <c r="O11" s="77" t="s">
+        <v>66</v>
+      </c>
+      <c r="P11" s="78"/>
+      <c r="Q11" s="78"/>
+      <c r="R11" s="78"/>
+      <c r="S11" s="78"/>
+      <c r="T11" s="78"/>
+      <c r="U11" s="79"/>
       <c r="V11" s="7"/>
       <c r="W11" s="3"/>
       <c r="X11" s="7"/>
-      <c r="Y11" s="57"/>
-      <c r="Z11" s="58"/>
+      <c r="Y11" s="46"/>
+      <c r="Z11" s="47"/>
     </row>
     <row r="12" spans="1:32" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A12" s="59"/>
-      <c r="B12" s="59"/>
-      <c r="C12" s="59"/>
+      <c r="A12" s="101"/>
+      <c r="B12" s="101"/>
+      <c r="C12" s="101"/>
       <c r="D12" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="54" t="s">
-        <v>132</v>
-      </c>
-      <c r="F12" s="56"/>
+        <v>39</v>
+      </c>
+      <c r="E12" s="77" t="s">
+        <v>127</v>
+      </c>
+      <c r="F12" s="79"/>
       <c r="G12" s="21"/>
       <c r="H12" s="22"/>
       <c r="I12" s="21"/>
-      <c r="J12" s="52"/>
+      <c r="J12" s="100"/>
       <c r="K12" s="23"/>
       <c r="L12" s="24"/>
       <c r="M12" s="25"/>
       <c r="N12" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="O12" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="P12" s="55"/>
-      <c r="Q12" s="55"/>
-      <c r="R12" s="55"/>
-      <c r="S12" s="55"/>
-      <c r="T12" s="55"/>
-      <c r="U12" s="56"/>
+        <v>39</v>
+      </c>
+      <c r="O12" s="77" t="s">
+        <v>67</v>
+      </c>
+      <c r="P12" s="78"/>
+      <c r="Q12" s="78"/>
+      <c r="R12" s="78"/>
+      <c r="S12" s="78"/>
+      <c r="T12" s="78"/>
+      <c r="U12" s="79"/>
       <c r="V12" s="7"/>
       <c r="W12" s="3"/>
       <c r="X12" s="7"/>
-      <c r="Y12" s="57"/>
-      <c r="Z12" s="58"/>
+      <c r="Y12" s="46"/>
+      <c r="Z12" s="47"/>
     </row>
     <row r="13" spans="1:32" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A13" s="59"/>
-      <c r="B13" s="59"/>
-      <c r="C13" s="59"/>
+      <c r="A13" s="101"/>
+      <c r="B13" s="101"/>
+      <c r="C13" s="101"/>
       <c r="D13" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="54" t="s">
-        <v>133</v>
-      </c>
-      <c r="F13" s="56"/>
+        <v>40</v>
+      </c>
+      <c r="E13" s="77" t="s">
+        <v>128</v>
+      </c>
+      <c r="F13" s="79"/>
       <c r="G13" s="21"/>
       <c r="H13" s="22"/>
       <c r="I13" s="21"/>
-      <c r="J13" s="52"/>
+      <c r="J13" s="100"/>
       <c r="K13" s="23"/>
       <c r="L13" s="24"/>
       <c r="M13" s="25"/>
       <c r="N13" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="O13" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="P13" s="55"/>
-      <c r="Q13" s="55"/>
-      <c r="R13" s="55"/>
-      <c r="S13" s="55"/>
-      <c r="T13" s="55"/>
-      <c r="U13" s="56"/>
+        <v>40</v>
+      </c>
+      <c r="O13" s="77" t="s">
+        <v>142</v>
+      </c>
+      <c r="P13" s="78"/>
+      <c r="Q13" s="78"/>
+      <c r="R13" s="78"/>
+      <c r="S13" s="78"/>
+      <c r="T13" s="78"/>
+      <c r="U13" s="79"/>
       <c r="V13" s="7"/>
       <c r="W13" s="3"/>
       <c r="X13" s="7"/>
-      <c r="Y13" s="57"/>
-      <c r="Z13" s="58"/>
+      <c r="Y13" s="46"/>
+      <c r="Z13" s="47"/>
     </row>
     <row r="14" spans="1:32" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A14" s="59"/>
-      <c r="B14" s="59"/>
-      <c r="C14" s="59"/>
+      <c r="A14" s="101"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="101"/>
       <c r="D14" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="53" t="s">
-        <v>134</v>
-      </c>
-      <c r="F14" s="53"/>
+        <v>41</v>
+      </c>
+      <c r="E14" s="60" t="s">
+        <v>129</v>
+      </c>
+      <c r="F14" s="60"/>
       <c r="G14" s="21"/>
       <c r="H14" s="22"/>
       <c r="I14" s="21"/>
-      <c r="J14" s="52"/>
+      <c r="J14" s="100"/>
       <c r="K14" s="23"/>
       <c r="L14" s="24"/>
       <c r="M14" s="25"/>
       <c r="N14" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="O14" s="64" t="s">
-        <v>157</v>
-      </c>
-      <c r="P14" s="55"/>
-      <c r="Q14" s="55"/>
-      <c r="R14" s="55"/>
-      <c r="S14" s="55"/>
-      <c r="T14" s="55"/>
-      <c r="U14" s="56"/>
+        <v>41</v>
+      </c>
+      <c r="O14" s="88" t="s">
+        <v>152</v>
+      </c>
+      <c r="P14" s="78"/>
+      <c r="Q14" s="78"/>
+      <c r="R14" s="78"/>
+      <c r="S14" s="78"/>
+      <c r="T14" s="78"/>
+      <c r="U14" s="79"/>
       <c r="V14" s="7"/>
       <c r="W14" s="3"/>
       <c r="X14" s="7"/>
-      <c r="Y14" s="87"/>
-      <c r="Z14" s="58"/>
+      <c r="Y14" s="45"/>
+      <c r="Z14" s="47"/>
       <c r="AF14"/>
     </row>
     <row r="15" spans="1:32" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A15" s="59"/>
-      <c r="B15" s="59"/>
-      <c r="C15" s="59"/>
+      <c r="A15" s="101"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="101"/>
       <c r="D15" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="54" t="s">
-        <v>135</v>
-      </c>
-      <c r="F15" s="56"/>
+        <v>42</v>
+      </c>
+      <c r="E15" s="77" t="s">
+        <v>130</v>
+      </c>
+      <c r="F15" s="79"/>
       <c r="G15" s="21"/>
       <c r="H15" s="22"/>
       <c r="I15" s="21"/>
-      <c r="J15" s="52"/>
+      <c r="J15" s="100"/>
       <c r="K15" s="23"/>
       <c r="L15" s="24"/>
       <c r="M15" s="25"/>
       <c r="N15" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="O15" s="64" t="s">
-        <v>85</v>
-      </c>
-      <c r="P15" s="55"/>
-      <c r="Q15" s="55"/>
-      <c r="R15" s="55"/>
-      <c r="S15" s="55"/>
-      <c r="T15" s="55"/>
-      <c r="U15" s="56"/>
+        <v>42</v>
+      </c>
+      <c r="O15" s="88" t="s">
+        <v>82</v>
+      </c>
+      <c r="P15" s="78"/>
+      <c r="Q15" s="78"/>
+      <c r="R15" s="78"/>
+      <c r="S15" s="78"/>
+      <c r="T15" s="78"/>
+      <c r="U15" s="79"/>
       <c r="V15" s="7"/>
       <c r="W15" s="3"/>
       <c r="X15" s="7"/>
-      <c r="Y15" s="57"/>
-      <c r="Z15" s="58"/>
+      <c r="Y15" s="46"/>
+      <c r="Z15" s="47"/>
     </row>
     <row r="16" spans="1:32" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A16" s="59"/>
-      <c r="B16" s="59"/>
-      <c r="C16" s="59"/>
+      <c r="A16" s="101"/>
+      <c r="B16" s="101"/>
+      <c r="C16" s="101"/>
       <c r="D16" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="54" t="s">
-        <v>136</v>
-      </c>
-      <c r="F16" s="56"/>
+        <v>43</v>
+      </c>
+      <c r="E16" s="77" t="s">
+        <v>131</v>
+      </c>
+      <c r="F16" s="79"/>
       <c r="G16" s="21"/>
       <c r="H16" s="22"/>
       <c r="I16" s="21"/>
-      <c r="J16" s="52"/>
+      <c r="J16" s="100"/>
       <c r="K16" s="23"/>
       <c r="L16" s="24"/>
       <c r="M16" s="25"/>
       <c r="N16" s="15">
         <v>2</v>
       </c>
-      <c r="O16" s="46" t="s">
-        <v>104</v>
-      </c>
-      <c r="P16" s="47"/>
-      <c r="Q16" s="47"/>
-      <c r="R16" s="47"/>
-      <c r="S16" s="47"/>
-      <c r="T16" s="47"/>
-      <c r="U16" s="48"/>
-      <c r="V16" s="65"/>
-      <c r="W16" s="66"/>
-      <c r="X16" s="67"/>
-      <c r="Y16" s="57"/>
-      <c r="Z16" s="58"/>
+      <c r="O16" s="84" t="s">
+        <v>101</v>
+      </c>
+      <c r="P16" s="87"/>
+      <c r="Q16" s="87"/>
+      <c r="R16" s="87"/>
+      <c r="S16" s="87"/>
+      <c r="T16" s="87"/>
+      <c r="U16" s="85"/>
+      <c r="V16" s="42"/>
+      <c r="W16" s="43"/>
+      <c r="X16" s="44"/>
+      <c r="Y16" s="46"/>
+      <c r="Z16" s="47"/>
     </row>
     <row r="17" spans="1:27" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A17" s="59"/>
-      <c r="B17" s="59"/>
-      <c r="C17" s="59"/>
+      <c r="A17" s="101"/>
+      <c r="B17" s="101"/>
+      <c r="C17" s="101"/>
       <c r="D17" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="54" t="s">
-        <v>137</v>
-      </c>
-      <c r="F17" s="56"/>
+        <v>44</v>
+      </c>
+      <c r="E17" s="77" t="s">
+        <v>132</v>
+      </c>
+      <c r="F17" s="79"/>
       <c r="G17" s="20"/>
       <c r="H17" s="28"/>
       <c r="I17" s="20"/>
-      <c r="J17" s="52"/>
+      <c r="J17" s="100"/>
       <c r="K17" s="23"/>
       <c r="L17" s="24"/>
       <c r="M17" s="25"/>
       <c r="N17" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="O17" s="54" t="s">
-        <v>148</v>
-      </c>
-      <c r="P17" s="55"/>
-      <c r="Q17" s="55"/>
-      <c r="R17" s="55"/>
-      <c r="S17" s="55"/>
-      <c r="T17" s="55"/>
-      <c r="U17" s="56"/>
+      <c r="O17" s="77" t="s">
+        <v>143</v>
+      </c>
+      <c r="P17" s="78"/>
+      <c r="Q17" s="78"/>
+      <c r="R17" s="78"/>
+      <c r="S17" s="78"/>
+      <c r="T17" s="78"/>
+      <c r="U17" s="79"/>
       <c r="V17" s="20"/>
       <c r="W17" s="28"/>
       <c r="X17" s="20"/>
-      <c r="Y17" s="57"/>
-      <c r="Z17" s="58"/>
+      <c r="Y17" s="46"/>
+      <c r="Z17" s="47"/>
     </row>
     <row r="18" spans="1:27" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A18" s="59"/>
-      <c r="B18" s="59"/>
-      <c r="C18" s="59"/>
+      <c r="A18" s="101"/>
+      <c r="B18" s="101"/>
+      <c r="C18" s="101"/>
       <c r="D18" s="15">
         <v>2</v>
       </c>
-      <c r="E18" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" s="42"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="66"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="52"/>
+      <c r="E18" s="82" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="82"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="100"/>
       <c r="K18" s="23"/>
       <c r="L18" s="24"/>
       <c r="M18" s="25"/>
       <c r="N18" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="O18" s="54" t="s">
-        <v>125</v>
-      </c>
-      <c r="P18" s="55"/>
-      <c r="Q18" s="55"/>
-      <c r="R18" s="55"/>
-      <c r="S18" s="55"/>
-      <c r="T18" s="55"/>
-      <c r="U18" s="56"/>
+      <c r="O18" s="77" t="s">
+        <v>120</v>
+      </c>
+      <c r="P18" s="78"/>
+      <c r="Q18" s="78"/>
+      <c r="R18" s="78"/>
+      <c r="S18" s="78"/>
+      <c r="T18" s="78"/>
+      <c r="U18" s="79"/>
       <c r="V18" s="7"/>
       <c r="W18" s="3"/>
       <c r="X18" s="7"/>
-      <c r="Y18" s="57"/>
-      <c r="Z18" s="58"/>
+      <c r="Y18" s="46"/>
+      <c r="Z18" s="47"/>
     </row>
     <row r="19" spans="1:27" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A19" s="59"/>
-      <c r="B19" s="59"/>
-      <c r="C19" s="59"/>
+      <c r="A19" s="101"/>
+      <c r="B19" s="101"/>
+      <c r="C19" s="101"/>
       <c r="D19" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E19" s="53" t="s">
-        <v>138</v>
-      </c>
-      <c r="F19" s="53"/>
+      <c r="E19" s="60" t="s">
+        <v>133</v>
+      </c>
+      <c r="F19" s="60"/>
       <c r="G19" s="20"/>
       <c r="H19" s="28"/>
       <c r="I19" s="20"/>
-      <c r="J19" s="52"/>
+      <c r="J19" s="100"/>
       <c r="K19" s="23"/>
       <c r="L19" s="24"/>
       <c r="M19" s="25"/>
       <c r="N19" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="O19" s="54" t="s">
-        <v>35</v>
-      </c>
-      <c r="P19" s="55"/>
-      <c r="Q19" s="55"/>
-      <c r="R19" s="55"/>
-      <c r="S19" s="55"/>
-      <c r="T19" s="55"/>
-      <c r="U19" s="56"/>
+        <v>45</v>
+      </c>
+      <c r="O19" s="77" t="s">
+        <v>33</v>
+      </c>
+      <c r="P19" s="78"/>
+      <c r="Q19" s="78"/>
+      <c r="R19" s="78"/>
+      <c r="S19" s="78"/>
+      <c r="T19" s="78"/>
+      <c r="U19" s="79"/>
       <c r="V19" s="20"/>
       <c r="W19" s="28"/>
       <c r="X19" s="20"/>
-      <c r="Y19" s="57"/>
-      <c r="Z19" s="58"/>
+      <c r="Y19" s="46"/>
+      <c r="Z19" s="47"/>
     </row>
     <row r="20" spans="1:27" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A20" s="59"/>
-      <c r="B20" s="59"/>
-      <c r="C20" s="59"/>
+      <c r="A20" s="101"/>
+      <c r="B20" s="101"/>
+      <c r="C20" s="101"/>
       <c r="D20" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" s="53"/>
+      <c r="E20" s="60" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="60"/>
       <c r="G20" s="7"/>
       <c r="H20" s="3"/>
       <c r="I20" s="7"/>
-      <c r="J20" s="52"/>
+      <c r="J20" s="100"/>
       <c r="K20" s="23"/>
       <c r="L20" s="24"/>
       <c r="M20" s="25"/>
       <c r="N20" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="O20" s="64" t="s">
-        <v>149</v>
-      </c>
-      <c r="P20" s="55"/>
-      <c r="Q20" s="55"/>
-      <c r="R20" s="55"/>
-      <c r="S20" s="55"/>
-      <c r="T20" s="55"/>
-      <c r="U20" s="56"/>
+        <v>46</v>
+      </c>
+      <c r="O20" s="88" t="s">
+        <v>144</v>
+      </c>
+      <c r="P20" s="78"/>
+      <c r="Q20" s="78"/>
+      <c r="R20" s="78"/>
+      <c r="S20" s="78"/>
+      <c r="T20" s="78"/>
+      <c r="U20" s="79"/>
       <c r="V20" s="7"/>
       <c r="W20" s="3"/>
       <c r="X20" s="7"/>
-      <c r="Y20" s="57"/>
-      <c r="Z20" s="58"/>
+      <c r="Y20" s="46"/>
+      <c r="Z20" s="47"/>
       <c r="AA20" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" spans="1:27" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A21" s="59"/>
-      <c r="B21" s="59"/>
-      <c r="C21" s="59"/>
+      <c r="A21" s="101"/>
+      <c r="B21" s="101"/>
+      <c r="C21" s="101"/>
       <c r="D21" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="F21" s="53"/>
+        <v>45</v>
+      </c>
+      <c r="E21" s="60" t="s">
+        <v>134</v>
+      </c>
+      <c r="F21" s="60"/>
       <c r="G21" s="7"/>
       <c r="H21" s="3"/>
       <c r="I21" s="7"/>
-      <c r="J21" s="52"/>
+      <c r="J21" s="100"/>
       <c r="K21" s="23"/>
       <c r="L21" s="24"/>
       <c r="M21" s="25"/>
       <c r="N21" s="15">
         <v>3</v>
       </c>
-      <c r="O21" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="P21" s="47"/>
-      <c r="Q21" s="47"/>
-      <c r="R21" s="47"/>
-      <c r="S21" s="47"/>
-      <c r="T21" s="47"/>
-      <c r="U21" s="48"/>
-      <c r="V21" s="65"/>
-      <c r="W21" s="66"/>
-      <c r="X21" s="67"/>
-      <c r="Y21" s="57"/>
-      <c r="Z21" s="58"/>
+      <c r="O21" s="84" t="s">
+        <v>90</v>
+      </c>
+      <c r="P21" s="87"/>
+      <c r="Q21" s="87"/>
+      <c r="R21" s="87"/>
+      <c r="S21" s="87"/>
+      <c r="T21" s="87"/>
+      <c r="U21" s="85"/>
+      <c r="V21" s="42"/>
+      <c r="W21" s="43"/>
+      <c r="X21" s="44"/>
+      <c r="Y21" s="46"/>
+      <c r="Z21" s="47"/>
     </row>
     <row r="22" spans="1:27" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A22" s="59"/>
-      <c r="B22" s="59"/>
-      <c r="C22" s="59"/>
+      <c r="A22" s="101"/>
+      <c r="B22" s="101"/>
+      <c r="C22" s="101"/>
       <c r="D22" s="15">
         <v>3</v>
       </c>
-      <c r="E22" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="42"/>
-      <c r="G22" s="87"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="52"/>
+      <c r="E22" s="82" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="82"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="100"/>
       <c r="K22" s="23"/>
       <c r="L22" s="24"/>
       <c r="N22" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="54" t="s">
-        <v>150</v>
-      </c>
-      <c r="P22" s="55"/>
-      <c r="Q22" s="55"/>
-      <c r="R22" s="55"/>
-      <c r="S22" s="55"/>
-      <c r="T22" s="55"/>
-      <c r="U22" s="56"/>
+      <c r="O22" s="77" t="s">
+        <v>145</v>
+      </c>
+      <c r="P22" s="78"/>
+      <c r="Q22" s="78"/>
+      <c r="R22" s="78"/>
+      <c r="S22" s="78"/>
+      <c r="T22" s="78"/>
+      <c r="U22" s="79"/>
       <c r="V22" s="20"/>
       <c r="W22" s="28"/>
       <c r="X22" s="20"/>
-      <c r="Y22" s="57"/>
-      <c r="Z22" s="58"/>
+      <c r="Y22" s="46"/>
+      <c r="Z22" s="47"/>
     </row>
     <row r="23" spans="1:27" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A23" s="59"/>
-      <c r="B23" s="59"/>
-      <c r="C23" s="59"/>
+      <c r="A23" s="101"/>
+      <c r="B23" s="101"/>
+      <c r="C23" s="101"/>
       <c r="D23" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="E23" s="53" t="s">
-        <v>140</v>
-      </c>
-      <c r="F23" s="53"/>
+      <c r="E23" s="60" t="s">
+        <v>135</v>
+      </c>
+      <c r="F23" s="60"/>
       <c r="G23" s="7"/>
       <c r="H23" s="3"/>
       <c r="I23" s="7"/>
-      <c r="J23" s="52"/>
+      <c r="J23" s="100"/>
       <c r="K23" s="23"/>
       <c r="L23" s="24"/>
       <c r="M23" s="25"/>
       <c r="N23" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="O23" s="54" t="s">
-        <v>151</v>
-      </c>
-      <c r="P23" s="55"/>
-      <c r="Q23" s="55"/>
-      <c r="R23" s="55"/>
-      <c r="S23" s="55"/>
-      <c r="T23" s="55"/>
-      <c r="U23" s="56"/>
+      <c r="O23" s="77" t="s">
+        <v>146</v>
+      </c>
+      <c r="P23" s="78"/>
+      <c r="Q23" s="78"/>
+      <c r="R23" s="78"/>
+      <c r="S23" s="78"/>
+      <c r="T23" s="78"/>
+      <c r="U23" s="79"/>
       <c r="V23" s="7"/>
       <c r="W23" s="3"/>
       <c r="X23" s="7"/>
-      <c r="Y23" s="57"/>
-      <c r="Z23" s="58"/>
+      <c r="Y23" s="46"/>
+      <c r="Z23" s="47"/>
     </row>
     <row r="24" spans="1:27" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A24" s="59"/>
-      <c r="B24" s="59"/>
-      <c r="C24" s="59"/>
+      <c r="A24" s="101"/>
+      <c r="B24" s="101"/>
+      <c r="C24" s="101"/>
       <c r="D24" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="53" t="s">
-        <v>67</v>
-      </c>
-      <c r="F24" s="53"/>
+      <c r="E24" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24" s="60"/>
       <c r="G24" s="7"/>
       <c r="H24" s="3"/>
       <c r="I24" s="7"/>
-      <c r="J24" s="52"/>
+      <c r="J24" s="100"/>
       <c r="K24" s="23"/>
       <c r="L24" s="24"/>
       <c r="M24" s="25"/>
       <c r="N24" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="O24" s="54" t="s">
-        <v>71</v>
-      </c>
-      <c r="P24" s="55"/>
-      <c r="Q24" s="55"/>
-      <c r="R24" s="55"/>
-      <c r="S24" s="55"/>
-      <c r="T24" s="55"/>
-      <c r="U24" s="56"/>
+        <v>47</v>
+      </c>
+      <c r="O24" s="77" t="s">
+        <v>68</v>
+      </c>
+      <c r="P24" s="78"/>
+      <c r="Q24" s="78"/>
+      <c r="R24" s="78"/>
+      <c r="S24" s="78"/>
+      <c r="T24" s="78"/>
+      <c r="U24" s="79"/>
       <c r="V24" s="7"/>
       <c r="W24" s="3"/>
       <c r="X24" s="7"/>
-      <c r="Y24" s="57"/>
-      <c r="Z24" s="58"/>
+      <c r="Y24" s="46"/>
+      <c r="Z24" s="47"/>
     </row>
     <row r="25" spans="1:27" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A25" s="59"/>
-      <c r="B25" s="59"/>
-      <c r="C25" s="59"/>
+      <c r="A25" s="101"/>
+      <c r="B25" s="101"/>
+      <c r="C25" s="101"/>
       <c r="D25" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" s="69" t="s">
-        <v>141</v>
-      </c>
-      <c r="F25" s="69"/>
+        <v>47</v>
+      </c>
+      <c r="E25" s="81" t="s">
+        <v>136</v>
+      </c>
+      <c r="F25" s="81"/>
       <c r="G25" s="7"/>
       <c r="H25" s="3"/>
       <c r="I25" s="7"/>
-      <c r="J25" s="52"/>
+      <c r="J25" s="100"/>
       <c r="K25" s="23"/>
       <c r="L25" s="24"/>
       <c r="M25" s="25"/>
       <c r="N25" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="O25" s="54" t="s">
-        <v>152</v>
-      </c>
-      <c r="P25" s="55"/>
-      <c r="Q25" s="55"/>
-      <c r="R25" s="55"/>
-      <c r="S25" s="55"/>
-      <c r="T25" s="55"/>
-      <c r="U25" s="56"/>
+      <c r="O25" s="77" t="s">
+        <v>147</v>
+      </c>
+      <c r="P25" s="78"/>
+      <c r="Q25" s="78"/>
+      <c r="R25" s="78"/>
+      <c r="S25" s="78"/>
+      <c r="T25" s="78"/>
+      <c r="U25" s="79"/>
       <c r="V25" s="7"/>
       <c r="W25" s="3"/>
       <c r="X25" s="7"/>
-      <c r="Y25" s="57"/>
-      <c r="Z25" s="58"/>
+      <c r="Y25" s="46"/>
+      <c r="Z25" s="47"/>
     </row>
     <row r="26" spans="1:27" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A26" s="59"/>
-      <c r="B26" s="59"/>
-      <c r="C26" s="59"/>
+      <c r="A26" s="101"/>
+      <c r="B26" s="101"/>
+      <c r="C26" s="101"/>
       <c r="D26" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="53" t="s">
-        <v>142</v>
-      </c>
-      <c r="F26" s="53"/>
+      <c r="E26" s="60" t="s">
+        <v>137</v>
+      </c>
+      <c r="F26" s="60"/>
       <c r="G26" s="7"/>
       <c r="H26" s="3"/>
       <c r="I26" s="7"/>
-      <c r="J26" s="52"/>
+      <c r="J26" s="100"/>
       <c r="K26" s="23"/>
       <c r="L26" s="24"/>
       <c r="M26" s="25"/>
       <c r="N26" s="15">
         <v>4</v>
       </c>
-      <c r="O26" s="70" t="s">
-        <v>32</v>
-      </c>
-      <c r="P26" s="70"/>
-      <c r="Q26" s="70"/>
-      <c r="R26" s="70"/>
-      <c r="S26" s="70"/>
-      <c r="T26" s="70"/>
-      <c r="U26" s="70"/>
-      <c r="V26" s="71"/>
-      <c r="W26" s="71"/>
-      <c r="X26" s="71"/>
-      <c r="Y26" s="68"/>
-      <c r="Z26" s="68"/>
+      <c r="O26" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="49"/>
+      <c r="R26" s="49"/>
+      <c r="S26" s="49"/>
+      <c r="T26" s="49"/>
+      <c r="U26" s="49"/>
+      <c r="V26" s="83"/>
+      <c r="W26" s="83"/>
+      <c r="X26" s="83"/>
+      <c r="Y26" s="59"/>
+      <c r="Z26" s="59"/>
     </row>
     <row r="27" spans="1:27" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A27" s="59"/>
-      <c r="B27" s="59"/>
-      <c r="C27" s="59"/>
+      <c r="A27" s="101"/>
+      <c r="B27" s="101"/>
+      <c r="C27" s="101"/>
       <c r="D27" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="F27" s="53"/>
+      <c r="E27" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="60"/>
       <c r="G27" s="7"/>
       <c r="H27" s="3"/>
       <c r="I27" s="7"/>
-      <c r="J27" s="52"/>
+      <c r="J27" s="100"/>
       <c r="K27" s="23"/>
       <c r="L27" s="24"/>
       <c r="M27" s="25"/>
       <c r="N27" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="O27" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="P27" s="53"/>
-      <c r="Q27" s="53"/>
-      <c r="R27" s="53"/>
-      <c r="S27" s="53"/>
-      <c r="T27" s="53"/>
-      <c r="U27" s="53"/>
+      <c r="O27" s="60" t="s">
+        <v>116</v>
+      </c>
+      <c r="P27" s="60"/>
+      <c r="Q27" s="60"/>
+      <c r="R27" s="60"/>
+      <c r="S27" s="60"/>
+      <c r="T27" s="60"/>
+      <c r="U27" s="60"/>
       <c r="V27" s="7"/>
       <c r="W27" s="3"/>
       <c r="X27" s="7"/>
-      <c r="Y27" s="68"/>
-      <c r="Z27" s="68"/>
+      <c r="Y27" s="59"/>
+      <c r="Z27" s="59"/>
     </row>
     <row r="28" spans="1:27" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A28" s="59"/>
-      <c r="B28" s="59"/>
-      <c r="C28" s="59"/>
+      <c r="A28" s="101"/>
+      <c r="B28" s="101"/>
+      <c r="C28" s="101"/>
       <c r="D28" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E28" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="F28" s="53"/>
+        <v>48</v>
+      </c>
+      <c r="E28" s="60" t="s">
+        <v>134</v>
+      </c>
+      <c r="F28" s="60"/>
       <c r="G28" s="7"/>
       <c r="H28" s="3"/>
       <c r="I28" s="7"/>
-      <c r="J28" s="52"/>
+      <c r="J28" s="100"/>
       <c r="K28" s="23"/>
       <c r="L28" s="24"/>
       <c r="M28" s="25"/>
       <c r="N28" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="O28" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="P28" s="53"/>
-      <c r="Q28" s="53"/>
-      <c r="R28" s="53"/>
-      <c r="S28" s="53"/>
-      <c r="T28" s="53"/>
-      <c r="U28" s="53"/>
+      <c r="O28" s="60" t="s">
+        <v>31</v>
+      </c>
+      <c r="P28" s="60"/>
+      <c r="Q28" s="60"/>
+      <c r="R28" s="60"/>
+      <c r="S28" s="60"/>
+      <c r="T28" s="60"/>
+      <c r="U28" s="60"/>
       <c r="V28" s="7"/>
       <c r="W28" s="3"/>
       <c r="X28" s="7"/>
-      <c r="Y28" s="68"/>
-      <c r="Z28" s="68"/>
+      <c r="Y28" s="59"/>
+      <c r="Z28" s="59"/>
     </row>
     <row r="29" spans="1:27" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A29" s="59"/>
-      <c r="B29" s="59"/>
-      <c r="C29" s="59"/>
+      <c r="A29" s="101"/>
+      <c r="B29" s="101"/>
+      <c r="C29" s="101"/>
       <c r="D29" s="15">
         <v>4</v>
       </c>
-      <c r="E29" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29" s="48"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="66"/>
-      <c r="I29" s="67"/>
-      <c r="J29" s="52"/>
+      <c r="E29" s="84" t="s">
+        <v>91</v>
+      </c>
+      <c r="F29" s="85"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="100"/>
       <c r="K29" s="23"/>
       <c r="L29" s="24"/>
       <c r="M29" s="25"/>
       <c r="N29" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="O29" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="P29" s="53"/>
-      <c r="Q29" s="53"/>
-      <c r="R29" s="53"/>
-      <c r="S29" s="53"/>
-      <c r="T29" s="53"/>
-      <c r="U29" s="53"/>
+        <v>49</v>
+      </c>
+      <c r="O29" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="P29" s="60"/>
+      <c r="Q29" s="60"/>
+      <c r="R29" s="60"/>
+      <c r="S29" s="60"/>
+      <c r="T29" s="60"/>
+      <c r="U29" s="60"/>
       <c r="V29" s="7"/>
       <c r="W29" s="3"/>
       <c r="X29" s="7"/>
-      <c r="Y29" s="68"/>
-      <c r="Z29" s="68"/>
+      <c r="Y29" s="59"/>
+      <c r="Z29" s="59"/>
     </row>
     <row r="30" spans="1:27" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A30" s="59"/>
-      <c r="B30" s="59"/>
-      <c r="C30" s="59"/>
+      <c r="A30" s="101"/>
+      <c r="B30" s="101"/>
+      <c r="C30" s="101"/>
       <c r="D30" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E30" s="53" t="s">
-        <v>76</v>
-      </c>
-      <c r="F30" s="53"/>
+      <c r="E30" s="60" t="s">
+        <v>73</v>
+      </c>
+      <c r="F30" s="60"/>
       <c r="G30" s="7"/>
       <c r="H30" s="3"/>
       <c r="I30" s="7"/>
-      <c r="J30" s="52"/>
+      <c r="J30" s="100"/>
       <c r="K30" s="23"/>
       <c r="L30" s="24"/>
       <c r="M30" s="25"/>
       <c r="N30" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="O30" s="53" t="s">
-        <v>153</v>
-      </c>
-      <c r="P30" s="53"/>
-      <c r="Q30" s="53"/>
-      <c r="R30" s="53"/>
-      <c r="S30" s="53"/>
-      <c r="T30" s="53"/>
-      <c r="U30" s="53"/>
+        <v>50</v>
+      </c>
+      <c r="O30" s="60" t="s">
+        <v>148</v>
+      </c>
+      <c r="P30" s="60"/>
+      <c r="Q30" s="60"/>
+      <c r="R30" s="60"/>
+      <c r="S30" s="60"/>
+      <c r="T30" s="60"/>
+      <c r="U30" s="60"/>
       <c r="V30" s="7"/>
       <c r="W30" s="3"/>
       <c r="X30" s="7"/>
-      <c r="Y30" s="68"/>
-      <c r="Z30" s="68"/>
+      <c r="Y30" s="59"/>
+      <c r="Z30" s="59"/>
     </row>
     <row r="31" spans="1:27" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A31" s="59"/>
-      <c r="B31" s="59"/>
-      <c r="C31" s="59"/>
+      <c r="A31" s="101"/>
+      <c r="B31" s="101"/>
+      <c r="C31" s="101"/>
       <c r="D31" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E31" s="72" t="s">
-        <v>143</v>
-      </c>
-      <c r="F31" s="53"/>
+      <c r="E31" s="86" t="s">
+        <v>138</v>
+      </c>
+      <c r="F31" s="60"/>
       <c r="G31" s="7"/>
       <c r="H31" s="3"/>
       <c r="I31" s="7"/>
-      <c r="J31" s="52"/>
+      <c r="J31" s="100"/>
       <c r="K31" s="23"/>
       <c r="L31" s="24"/>
       <c r="M31" s="25"/>
       <c r="N31" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="O31" s="53" t="s">
-        <v>74</v>
-      </c>
-      <c r="P31" s="53"/>
-      <c r="Q31" s="53"/>
-      <c r="R31" s="53"/>
-      <c r="S31" s="53"/>
-      <c r="T31" s="53"/>
-      <c r="U31" s="53"/>
+        <v>51</v>
+      </c>
+      <c r="O31" s="60" t="s">
+        <v>71</v>
+      </c>
+      <c r="P31" s="60"/>
+      <c r="Q31" s="60"/>
+      <c r="R31" s="60"/>
+      <c r="S31" s="60"/>
+      <c r="T31" s="60"/>
+      <c r="U31" s="60"/>
       <c r="V31" s="7"/>
       <c r="W31" s="3"/>
       <c r="X31" s="7"/>
-      <c r="Y31" s="68"/>
-      <c r="Z31" s="68"/>
+      <c r="Y31" s="59"/>
+      <c r="Z31" s="59"/>
     </row>
     <row r="32" spans="1:27" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A32" s="60" t="s">
-        <v>99</v>
-      </c>
-      <c r="B32" s="60"/>
-      <c r="C32" s="60"/>
+      <c r="A32" s="102" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="102"/>
+      <c r="C32" s="102"/>
       <c r="D32" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E32" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="F32" s="53"/>
+        <v>49</v>
+      </c>
+      <c r="E32" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32" s="60"/>
       <c r="G32" s="7"/>
       <c r="H32" s="3"/>
       <c r="I32" s="7"/>
-      <c r="J32" s="52"/>
+      <c r="J32" s="100"/>
       <c r="K32" s="23"/>
       <c r="L32" s="24"/>
       <c r="M32" s="25"/>
       <c r="N32" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="O32" s="53" t="s">
-        <v>73</v>
-      </c>
-      <c r="P32" s="53"/>
-      <c r="Q32" s="53"/>
-      <c r="R32" s="53"/>
-      <c r="S32" s="53"/>
-      <c r="T32" s="53"/>
-      <c r="U32" s="53"/>
+        <v>55</v>
+      </c>
+      <c r="O32" s="60" t="s">
+        <v>70</v>
+      </c>
+      <c r="P32" s="60"/>
+      <c r="Q32" s="60"/>
+      <c r="R32" s="60"/>
+      <c r="S32" s="60"/>
+      <c r="T32" s="60"/>
+      <c r="U32" s="60"/>
       <c r="V32" s="7"/>
       <c r="W32" s="3"/>
       <c r="X32" s="7"/>
-      <c r="Y32" s="68"/>
-      <c r="Z32" s="68"/>
+      <c r="Y32" s="59"/>
+      <c r="Z32" s="59"/>
     </row>
     <row r="33" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A33" s="61" t="s">
-        <v>100</v>
-      </c>
-      <c r="B33" s="61"/>
-      <c r="C33" s="61"/>
+      <c r="A33" s="103" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" s="103"/>
+      <c r="C33" s="103"/>
       <c r="D33" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E33" s="53" t="s">
-        <v>144</v>
-      </c>
-      <c r="F33" s="53"/>
+        <v>50</v>
+      </c>
+      <c r="E33" s="60" t="s">
+        <v>139</v>
+      </c>
+      <c r="F33" s="60"/>
       <c r="G33" s="20"/>
       <c r="H33" s="28"/>
       <c r="I33" s="20"/>
-      <c r="J33" s="52"/>
+      <c r="J33" s="100"/>
       <c r="K33" s="23"/>
       <c r="L33" s="24"/>
       <c r="M33" s="25"/>
       <c r="N33" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="O33" s="53" t="s">
-        <v>123</v>
-      </c>
-      <c r="P33" s="53"/>
-      <c r="Q33" s="53"/>
-      <c r="R33" s="53"/>
-      <c r="S33" s="53"/>
-      <c r="T33" s="53"/>
-      <c r="U33" s="53"/>
+        <v>56</v>
+      </c>
+      <c r="O33" s="60" t="s">
+        <v>118</v>
+      </c>
+      <c r="P33" s="60"/>
+      <c r="Q33" s="60"/>
+      <c r="R33" s="60"/>
+      <c r="S33" s="60"/>
+      <c r="T33" s="60"/>
+      <c r="U33" s="60"/>
       <c r="V33" s="20"/>
       <c r="W33" s="28"/>
       <c r="X33" s="20"/>
-      <c r="Y33" s="68"/>
-      <c r="Z33" s="68"/>
+      <c r="Y33" s="59"/>
+      <c r="Z33" s="59"/>
     </row>
     <row r="34" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A34" s="62" t="s">
-        <v>101</v>
-      </c>
-      <c r="B34" s="62"/>
-      <c r="C34" s="62"/>
+      <c r="A34" s="104" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" s="104"/>
+      <c r="C34" s="104"/>
       <c r="D34" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E34" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="F34" s="53"/>
+        <v>51</v>
+      </c>
+      <c r="E34" s="60" t="s">
+        <v>140</v>
+      </c>
+      <c r="F34" s="60"/>
       <c r="G34" s="7"/>
       <c r="H34" s="3"/>
       <c r="I34" s="7"/>
-      <c r="J34" s="52"/>
+      <c r="J34" s="100"/>
       <c r="K34" s="23"/>
       <c r="L34" s="24"/>
       <c r="M34" s="25"/>
-      <c r="N34" s="68"/>
-      <c r="O34" s="68"/>
-      <c r="P34" s="68"/>
-      <c r="Q34" s="68"/>
-      <c r="R34" s="68"/>
-      <c r="S34" s="68"/>
-      <c r="T34" s="68"/>
-      <c r="U34" s="68"/>
-      <c r="V34" s="68"/>
-      <c r="W34" s="68"/>
-      <c r="X34" s="68"/>
-      <c r="Y34" s="68"/>
-      <c r="Z34" s="68"/>
+      <c r="N34" s="59"/>
+      <c r="O34" s="59"/>
+      <c r="P34" s="59"/>
+      <c r="Q34" s="59"/>
+      <c r="R34" s="59"/>
+      <c r="S34" s="59"/>
+      <c r="T34" s="59"/>
+      <c r="U34" s="59"/>
+      <c r="V34" s="59"/>
+      <c r="W34" s="59"/>
+      <c r="X34" s="59"/>
+      <c r="Y34" s="59"/>
+      <c r="Z34" s="59"/>
     </row>
     <row r="35" spans="1:26" s="1" customFormat="1" ht="7.5" customHeight="1">
-      <c r="A35" s="98"/>
-      <c r="B35" s="99"/>
-      <c r="C35" s="99"/>
-      <c r="D35" s="99"/>
-      <c r="E35" s="99"/>
-      <c r="F35" s="99"/>
-      <c r="G35" s="99"/>
-      <c r="H35" s="99"/>
-      <c r="I35" s="99"/>
-      <c r="J35" s="100"/>
-      <c r="K35" s="99"/>
-      <c r="L35" s="99"/>
-      <c r="M35" s="99"/>
-      <c r="N35" s="99"/>
-      <c r="O35" s="99"/>
-      <c r="P35" s="99"/>
-      <c r="Q35" s="99"/>
-      <c r="R35" s="99"/>
-      <c r="S35" s="99"/>
-      <c r="T35" s="99"/>
-      <c r="U35" s="99"/>
-      <c r="V35" s="99"/>
-      <c r="W35" s="99"/>
-      <c r="X35" s="99"/>
-      <c r="Y35" s="99"/>
-      <c r="Z35" s="101"/>
+      <c r="A35" s="61"/>
+      <c r="B35" s="62"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="62"/>
+      <c r="F35" s="62"/>
+      <c r="G35" s="62"/>
+      <c r="H35" s="62"/>
+      <c r="I35" s="62"/>
+      <c r="J35" s="63"/>
+      <c r="K35" s="62"/>
+      <c r="L35" s="62"/>
+      <c r="M35" s="62"/>
+      <c r="N35" s="62"/>
+      <c r="O35" s="62"/>
+      <c r="P35" s="62"/>
+      <c r="Q35" s="62"/>
+      <c r="R35" s="62"/>
+      <c r="S35" s="62"/>
+      <c r="T35" s="62"/>
+      <c r="U35" s="62"/>
+      <c r="V35" s="62"/>
+      <c r="W35" s="62"/>
+      <c r="X35" s="62"/>
+      <c r="Y35" s="62"/>
+      <c r="Z35" s="64"/>
     </row>
     <row r="36" spans="1:26" s="1" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A36" s="89" t="s">
-        <v>88</v>
-      </c>
-      <c r="B36" s="90"/>
-      <c r="C36" s="90"/>
-      <c r="D36" s="90"/>
-      <c r="E36" s="90"/>
-      <c r="F36" s="90"/>
-      <c r="G36" s="90"/>
-      <c r="H36" s="90"/>
-      <c r="I36" s="90"/>
-      <c r="J36" s="90"/>
-      <c r="K36" s="90"/>
-      <c r="L36" s="90"/>
-      <c r="M36" s="90"/>
-      <c r="N36" s="90"/>
-      <c r="O36" s="90"/>
-      <c r="P36" s="90"/>
-      <c r="Q36" s="90"/>
-      <c r="R36" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="S36" s="37"/>
-      <c r="T36" s="37"/>
-      <c r="U36" s="37"/>
-      <c r="V36" s="37"/>
-      <c r="W36" s="37"/>
+      <c r="A36" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
+      <c r="J36" s="51"/>
+      <c r="K36" s="51"/>
+      <c r="L36" s="51"/>
+      <c r="M36" s="51"/>
+      <c r="N36" s="51"/>
+      <c r="O36" s="51"/>
+      <c r="P36" s="51"/>
+      <c r="Q36" s="51"/>
+      <c r="R36" s="93" t="s">
+        <v>92</v>
+      </c>
+      <c r="S36" s="93"/>
+      <c r="T36" s="93"/>
+      <c r="U36" s="93"/>
+      <c r="V36" s="93"/>
+      <c r="W36" s="93"/>
       <c r="X36" s="29" t="s">
         <v>1</v>
       </c>
@@ -6822,35 +6819,35 @@
         <v>2</v>
       </c>
       <c r="Z36" s="31" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:26" s="1" customFormat="1" ht="24.9" customHeight="1">
-      <c r="A37" s="91"/>
-      <c r="B37" s="92"/>
-      <c r="C37" s="92"/>
-      <c r="D37" s="92"/>
-      <c r="E37" s="92"/>
-      <c r="F37" s="92"/>
-      <c r="G37" s="92"/>
-      <c r="H37" s="92"/>
-      <c r="I37" s="92"/>
-      <c r="J37" s="92"/>
-      <c r="K37" s="92"/>
-      <c r="L37" s="92"/>
-      <c r="M37" s="92"/>
-      <c r="N37" s="92"/>
-      <c r="O37" s="92"/>
-      <c r="P37" s="92"/>
-      <c r="Q37" s="92"/>
-      <c r="R37" s="38" t="s">
-        <v>158</v>
-      </c>
-      <c r="S37" s="38"/>
-      <c r="T37" s="38"/>
-      <c r="U37" s="38"/>
-      <c r="V37" s="38"/>
-      <c r="W37" s="38"/>
+      <c r="A37" s="52"/>
+      <c r="B37" s="53"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="53"/>
+      <c r="N37" s="53"/>
+      <c r="O37" s="53"/>
+      <c r="P37" s="53"/>
+      <c r="Q37" s="53"/>
+      <c r="R37" s="94" t="s">
+        <v>153</v>
+      </c>
+      <c r="S37" s="94"/>
+      <c r="T37" s="94"/>
+      <c r="U37" s="94"/>
+      <c r="V37" s="94"/>
+      <c r="W37" s="94"/>
       <c r="X37" s="30" t="s">
         <v>1</v>
       </c>
@@ -6858,105 +6855,207 @@
         <v>2</v>
       </c>
       <c r="Z37" s="32" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:26" s="1" customFormat="1" ht="78.900000000000006" customHeight="1">
-      <c r="A38" s="86" t="s">
-        <v>159</v>
-      </c>
-      <c r="B38" s="86"/>
-      <c r="C38" s="86"/>
-      <c r="D38" s="86"/>
-      <c r="E38" s="86"/>
-      <c r="F38" s="86"/>
-      <c r="G38" s="86"/>
-      <c r="H38" s="86"/>
-      <c r="I38" s="86"/>
-      <c r="J38" s="86"/>
-      <c r="K38" s="86"/>
-      <c r="L38" s="86"/>
-      <c r="M38" s="86"/>
-      <c r="N38" s="86"/>
-      <c r="O38" s="86"/>
-      <c r="P38" s="86"/>
-      <c r="Q38" s="86"/>
-      <c r="R38" s="86"/>
-      <c r="S38" s="86"/>
-      <c r="T38" s="86"/>
-      <c r="U38" s="86"/>
-      <c r="V38" s="86"/>
-      <c r="W38" s="86"/>
-      <c r="X38" s="86"/>
-      <c r="Y38" s="86"/>
-      <c r="Z38" s="86"/>
+      <c r="A38" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="B38" s="41"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="41"/>
+      <c r="I38" s="41"/>
+      <c r="J38" s="41"/>
+      <c r="K38" s="41"/>
+      <c r="L38" s="41"/>
+      <c r="M38" s="41"/>
+      <c r="N38" s="41"/>
+      <c r="O38" s="41"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="41"/>
+      <c r="S38" s="41"/>
+      <c r="T38" s="41"/>
+      <c r="U38" s="41"/>
+      <c r="V38" s="41"/>
+      <c r="W38" s="41"/>
+      <c r="X38" s="41"/>
+      <c r="Y38" s="41"/>
+      <c r="Z38" s="41"/>
     </row>
     <row r="39" spans="1:26" s="1" customFormat="1" ht="5.4" customHeight="1">
-      <c r="A39" s="41"/>
-      <c r="B39" s="41"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="41"/>
-      <c r="I39" s="41"/>
-      <c r="J39" s="41"/>
-      <c r="K39" s="41"/>
-      <c r="L39" s="41"/>
-      <c r="M39" s="41"/>
-      <c r="N39" s="41"/>
-      <c r="O39" s="41"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="41"/>
-      <c r="S39" s="41"/>
-      <c r="T39" s="41"/>
-      <c r="U39" s="41"/>
-      <c r="V39" s="41"/>
-      <c r="W39" s="41"/>
-      <c r="X39" s="41"/>
-      <c r="Y39" s="41"/>
-      <c r="Z39" s="41"/>
+      <c r="A39" s="97"/>
+      <c r="B39" s="97"/>
+      <c r="C39" s="97"/>
+      <c r="D39" s="97"/>
+      <c r="E39" s="97"/>
+      <c r="F39" s="97"/>
+      <c r="G39" s="97"/>
+      <c r="H39" s="97"/>
+      <c r="I39" s="97"/>
+      <c r="J39" s="97"/>
+      <c r="K39" s="97"/>
+      <c r="L39" s="97"/>
+      <c r="M39" s="97"/>
+      <c r="N39" s="97"/>
+      <c r="O39" s="97"/>
+      <c r="P39" s="97"/>
+      <c r="Q39" s="97"/>
+      <c r="R39" s="97"/>
+      <c r="S39" s="97"/>
+      <c r="T39" s="97"/>
+      <c r="U39" s="97"/>
+      <c r="V39" s="97"/>
+      <c r="W39" s="97"/>
+      <c r="X39" s="97"/>
+      <c r="Y39" s="97"/>
+      <c r="Z39" s="97"/>
     </row>
     <row r="40" spans="1:26" ht="44.1" customHeight="1">
-      <c r="A40" s="88" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="88"/>
-      <c r="C40" s="88"/>
-      <c r="D40" s="96"/>
-      <c r="E40" s="97"/>
+      <c r="A40" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="48"/>
+      <c r="C40" s="48"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="58"/>
       <c r="F40" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="G40" s="85"/>
-      <c r="H40" s="85"/>
-      <c r="I40" s="85"/>
-      <c r="J40" s="85"/>
-      <c r="K40" s="85"/>
-      <c r="L40" s="85"/>
+        <v>72</v>
+      </c>
+      <c r="G40" s="40"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="40"/>
+      <c r="J40" s="40"/>
+      <c r="K40" s="40"/>
+      <c r="L40" s="40"/>
       <c r="M40" s="9"/>
-      <c r="N40" s="70" t="s">
-        <v>40</v>
-      </c>
-      <c r="O40" s="70"/>
-      <c r="P40" s="70"/>
-      <c r="Q40" s="93"/>
-      <c r="R40" s="94"/>
-      <c r="S40" s="94"/>
-      <c r="T40" s="94"/>
-      <c r="U40" s="94"/>
-      <c r="V40" s="94"/>
-      <c r="W40" s="95"/>
-      <c r="X40" s="70" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y40" s="70"/>
+      <c r="N40" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="O40" s="49"/>
+      <c r="P40" s="49"/>
+      <c r="Q40" s="54"/>
+      <c r="R40" s="55"/>
+      <c r="S40" s="55"/>
+      <c r="T40" s="55"/>
+      <c r="U40" s="55"/>
+      <c r="V40" s="55"/>
+      <c r="W40" s="56"/>
+      <c r="X40" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y40" s="49"/>
       <c r="Z40" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="126">
+    <mergeCell ref="R36:W36"/>
+    <mergeCell ref="R37:W37"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="A39:Z39"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="O8:U8"/>
+    <mergeCell ref="A5:Z5"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J6:J34"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="O11:U11"/>
+    <mergeCell ref="Y11:Z11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="O12:U12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:C31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="O13:U13"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="O9:U9"/>
+    <mergeCell ref="Y9:Z9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="O10:U10"/>
+    <mergeCell ref="Y10:Z10"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="O17:U17"/>
+    <mergeCell ref="Y17:Z17"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="O18:U18"/>
+    <mergeCell ref="Y18:Z18"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="O14:U14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="O15:U15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="O16:U16"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="O21:U21"/>
+    <mergeCell ref="Y21:Z21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="O22:U22"/>
+    <mergeCell ref="Y22:Z22"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O19:U19"/>
+    <mergeCell ref="Y19:Z19"/>
+    <mergeCell ref="O20:U20"/>
+    <mergeCell ref="Y20:Z20"/>
+    <mergeCell ref="N34:Z34"/>
+    <mergeCell ref="Y25:Z25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="O26:U26"/>
+    <mergeCell ref="Y26:Z26"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="O23:U23"/>
+    <mergeCell ref="Y23:Z23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="O24:U24"/>
+    <mergeCell ref="Y24:Z24"/>
+    <mergeCell ref="V26:X26"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="O30:U30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="Y29:Z29"/>
+    <mergeCell ref="Y30:Z30"/>
+    <mergeCell ref="O31:U31"/>
+    <mergeCell ref="Y31:Z31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="O32:U32"/>
+    <mergeCell ref="Y32:Z32"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:X2"/>
+    <mergeCell ref="W4:Y4"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="Y28:Z28"/>
+    <mergeCell ref="Y12:Z12"/>
+    <mergeCell ref="Y13:Z13"/>
+    <mergeCell ref="Y14:Z14"/>
+    <mergeCell ref="Y15:Z15"/>
+    <mergeCell ref="Y16:Z16"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="O27:U27"/>
+    <mergeCell ref="K7:U7"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="K6:X6"/>
+    <mergeCell ref="Y6:Z8"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="O25:U25"/>
+    <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="G40:L40"/>
     <mergeCell ref="A38:Z38"/>
@@ -6981,108 +7080,6 @@
     <mergeCell ref="O33:U33"/>
     <mergeCell ref="Y33:Z33"/>
     <mergeCell ref="E33:F33"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:X2"/>
-    <mergeCell ref="W4:Y4"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="Y28:Z28"/>
-    <mergeCell ref="Y12:Z12"/>
-    <mergeCell ref="Y13:Z13"/>
-    <mergeCell ref="Y14:Z14"/>
-    <mergeCell ref="Y15:Z15"/>
-    <mergeCell ref="Y16:Z16"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="O27:U27"/>
-    <mergeCell ref="K7:U7"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="K6:X6"/>
-    <mergeCell ref="Y6:Z8"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="O25:U25"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="N34:Z34"/>
-    <mergeCell ref="Y25:Z25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="O26:U26"/>
-    <mergeCell ref="Y26:Z26"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="O23:U23"/>
-    <mergeCell ref="Y23:Z23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="O24:U24"/>
-    <mergeCell ref="Y24:Z24"/>
-    <mergeCell ref="V26:X26"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="O30:U30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="Y29:Z29"/>
-    <mergeCell ref="Y30:Z30"/>
-    <mergeCell ref="O31:U31"/>
-    <mergeCell ref="Y31:Z31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="O32:U32"/>
-    <mergeCell ref="Y32:Z32"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="O21:U21"/>
-    <mergeCell ref="Y21:Z21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="O22:U22"/>
-    <mergeCell ref="Y22:Z22"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O19:U19"/>
-    <mergeCell ref="Y19:Z19"/>
-    <mergeCell ref="O20:U20"/>
-    <mergeCell ref="Y20:Z20"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="O18:U18"/>
-    <mergeCell ref="Y18:Z18"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="O14:U14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="O15:U15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="O16:U16"/>
-    <mergeCell ref="V16:X16"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="O9:U9"/>
-    <mergeCell ref="Y9:Z9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="O10:U10"/>
-    <mergeCell ref="Y10:Z10"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="O17:U17"/>
-    <mergeCell ref="Y17:Z17"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="R36:W36"/>
-    <mergeCell ref="R37:W37"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="A39:Z39"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="O8:U8"/>
-    <mergeCell ref="A5:Z5"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J6:J34"/>
-    <mergeCell ref="V7:X7"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="O11:U11"/>
-    <mergeCell ref="Y11:Z11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="O12:U12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:C31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="O13:U13"/>
-    <mergeCell ref="E9:F9"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -7126,66 +7123,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="36.9" customHeight="1" thickBot="1">
-      <c r="A1" s="73"/>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="74" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="74"/>
-      <c r="U1" s="74"/>
-      <c r="V1" s="74"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="74"/>
-      <c r="Y1" s="39" t="s">
-        <v>154</v>
-      </c>
-      <c r="Z1" s="39"/>
+      <c r="A1" s="65"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="66" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="66"/>
+      <c r="T1" s="66"/>
+      <c r="U1" s="66"/>
+      <c r="V1" s="66"/>
+      <c r="W1" s="66"/>
+      <c r="X1" s="66"/>
+      <c r="Y1" s="95" t="s">
+        <v>149</v>
+      </c>
+      <c r="Z1" s="95"/>
     </row>
     <row r="2" spans="1:29" ht="27" customHeight="1" thickBot="1">
-      <c r="A2" s="73"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
-      <c r="N2" s="74"/>
-      <c r="O2" s="74"/>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="74"/>
-      <c r="S2" s="74"/>
-      <c r="T2" s="74"/>
-      <c r="U2" s="74"/>
-      <c r="V2" s="74"/>
-      <c r="W2" s="74"/>
-      <c r="X2" s="74"/>
-      <c r="Y2" s="40" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="66"/>
+      <c r="Q2" s="66"/>
+      <c r="R2" s="66"/>
+      <c r="S2" s="66"/>
+      <c r="T2" s="66"/>
+      <c r="U2" s="66"/>
+      <c r="V2" s="66"/>
+      <c r="W2" s="66"/>
+      <c r="X2" s="66"/>
+      <c r="Y2" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="Z2" s="40"/>
+      <c r="Z2" s="96"/>
     </row>
     <row r="3" spans="1:29" ht="8.4" customHeight="1">
       <c r="D3" s="6"/>
@@ -7213,150 +7210,150 @@
       <c r="Z3" s="2"/>
     </row>
     <row r="4" spans="1:29" ht="34.5" customHeight="1">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="93"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="95"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
-      <c r="K4" s="76"/>
-      <c r="L4" s="70" t="s">
+      <c r="B4" s="85"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="M4" s="70"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="75"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
       <c r="T4" s="11"/>
       <c r="U4" s="11"/>
       <c r="V4" s="17"/>
-      <c r="W4" s="70" t="s">
+      <c r="W4" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="X4" s="70"/>
-      <c r="Y4" s="70"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
       <c r="Z4" s="18"/>
     </row>
     <row r="5" spans="1:29" ht="6.6" customHeight="1">
-      <c r="A5" s="49"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="50"/>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
-      <c r="T5" s="50"/>
-      <c r="U5" s="50"/>
-      <c r="V5" s="50"/>
-      <c r="W5" s="50"/>
-      <c r="X5" s="50"/>
-      <c r="Y5" s="50"/>
-      <c r="Z5" s="50"/>
+      <c r="A5" s="98"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="99"/>
+      <c r="H5" s="99"/>
+      <c r="I5" s="99"/>
+      <c r="J5" s="98"/>
+      <c r="K5" s="99"/>
+      <c r="L5" s="99"/>
+      <c r="M5" s="99"/>
+      <c r="N5" s="99"/>
+      <c r="O5" s="99"/>
+      <c r="P5" s="99"/>
+      <c r="Q5" s="99"/>
+      <c r="R5" s="99"/>
+      <c r="S5" s="99"/>
+      <c r="T5" s="99"/>
+      <c r="U5" s="99"/>
+      <c r="V5" s="99"/>
+      <c r="W5" s="99"/>
+      <c r="X5" s="99"/>
+      <c r="Y5" s="99"/>
+      <c r="Z5" s="99"/>
     </row>
     <row r="6" spans="1:29" ht="27.75" customHeight="1">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
+      <c r="P6" s="69"/>
+      <c r="Q6" s="69"/>
+      <c r="R6" s="69"/>
+      <c r="S6" s="69"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="69"/>
+      <c r="V6" s="69"/>
+      <c r="W6" s="69"/>
+      <c r="X6" s="69"/>
+      <c r="Y6" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="51"/>
-      <c r="S6" s="51"/>
-      <c r="T6" s="51"/>
-      <c r="U6" s="51"/>
-      <c r="V6" s="51"/>
-      <c r="W6" s="51"/>
-      <c r="X6" s="51"/>
-      <c r="Y6" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z6" s="51"/>
+      <c r="Z6" s="69"/>
     </row>
     <row r="7" spans="1:29" ht="37.5" customHeight="1">
-      <c r="A7" s="51" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51" t="s">
+      <c r="A7" s="69" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="69"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="L7" s="51"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="51"/>
-      <c r="S7" s="51"/>
-      <c r="T7" s="51"/>
-      <c r="U7" s="51"/>
-      <c r="V7" s="51" t="s">
+      <c r="H7" s="69"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="69" t="s">
+        <v>150</v>
+      </c>
+      <c r="L7" s="69"/>
+      <c r="M7" s="69"/>
+      <c r="N7" s="69"/>
+      <c r="O7" s="69"/>
+      <c r="P7" s="69"/>
+      <c r="Q7" s="69"/>
+      <c r="R7" s="69"/>
+      <c r="S7" s="69"/>
+      <c r="T7" s="69"/>
+      <c r="U7" s="69"/>
+      <c r="V7" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="W7" s="51"/>
-      <c r="X7" s="51"/>
-      <c r="Y7" s="51"/>
-      <c r="Z7" s="51"/>
+      <c r="W7" s="69"/>
+      <c r="X7" s="69"/>
+      <c r="Y7" s="69"/>
+      <c r="Z7" s="69"/>
     </row>
     <row r="8" spans="1:29" s="1" customFormat="1" ht="32.1" customHeight="1">
-      <c r="A8" s="84" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" s="84"/>
-      <c r="C8" s="84"/>
+      <c r="A8" s="80" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" s="80"/>
+      <c r="C8" s="80"/>
       <c r="D8" s="15">
         <v>1</v>
       </c>
-      <c r="E8" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="48"/>
+      <c r="E8" s="84" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="85"/>
       <c r="G8" s="8" t="s">
         <v>1</v>
       </c>
@@ -7366,24 +7363,24 @@
       <c r="I8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J8" s="52"/>
-      <c r="K8" s="43" t="s">
-        <v>108</v>
-      </c>
-      <c r="L8" s="44"/>
-      <c r="M8" s="45"/>
+      <c r="J8" s="100"/>
+      <c r="K8" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="L8" s="38"/>
+      <c r="M8" s="39"/>
       <c r="N8" s="12">
         <v>1</v>
       </c>
-      <c r="O8" s="102" t="s">
-        <v>87</v>
-      </c>
-      <c r="P8" s="103"/>
-      <c r="Q8" s="103"/>
-      <c r="R8" s="103"/>
-      <c r="S8" s="103"/>
-      <c r="T8" s="103"/>
-      <c r="U8" s="104"/>
+      <c r="O8" s="126" t="s">
+        <v>84</v>
+      </c>
+      <c r="P8" s="127"/>
+      <c r="Q8" s="127"/>
+      <c r="R8" s="127"/>
+      <c r="S8" s="127"/>
+      <c r="T8" s="127"/>
+      <c r="U8" s="128"/>
       <c r="V8" s="8" t="s">
         <v>1</v>
       </c>
@@ -7393,993 +7390,993 @@
       <c r="X8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="Y8" s="51"/>
-      <c r="Z8" s="51"/>
+      <c r="Y8" s="69"/>
+      <c r="Z8" s="69"/>
     </row>
     <row r="9" spans="1:29" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A9" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="45"/>
+      <c r="A9" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" s="38"/>
+      <c r="C9" s="39"/>
       <c r="D9" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="54" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="56"/>
+      <c r="E9" s="77" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="79"/>
       <c r="G9" s="7"/>
       <c r="H9" s="3"/>
       <c r="I9" s="7"/>
-      <c r="J9" s="52"/>
-      <c r="K9" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="L9" s="44"/>
-      <c r="M9" s="45"/>
+      <c r="J9" s="100"/>
+      <c r="K9" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="L9" s="38"/>
+      <c r="M9" s="39"/>
       <c r="N9" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="54" t="s">
-        <v>30</v>
-      </c>
-      <c r="P9" s="55"/>
-      <c r="Q9" s="55"/>
-      <c r="R9" s="55"/>
-      <c r="S9" s="55"/>
-      <c r="T9" s="55"/>
-      <c r="U9" s="56"/>
+      <c r="O9" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="P9" s="78"/>
+      <c r="Q9" s="78"/>
+      <c r="R9" s="78"/>
+      <c r="S9" s="78"/>
+      <c r="T9" s="78"/>
+      <c r="U9" s="79"/>
       <c r="V9" s="33"/>
       <c r="W9" s="34"/>
       <c r="X9" s="33"/>
-      <c r="Y9" s="57"/>
-      <c r="Z9" s="58"/>
+      <c r="Y9" s="46"/>
+      <c r="Z9" s="47"/>
     </row>
     <row r="10" spans="1:29" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A10" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="44"/>
-      <c r="C10" s="45"/>
+      <c r="A10" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="B10" s="38"/>
+      <c r="C10" s="39"/>
       <c r="D10" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="54" t="s">
-        <v>118</v>
-      </c>
-      <c r="F10" s="56"/>
+      <c r="E10" s="77" t="s">
+        <v>113</v>
+      </c>
+      <c r="F10" s="79"/>
       <c r="G10" s="7"/>
       <c r="H10" s="3"/>
       <c r="I10" s="7"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="43" t="s">
-        <v>59</v>
-      </c>
-      <c r="L10" s="44"/>
-      <c r="M10" s="45"/>
+      <c r="J10" s="100"/>
+      <c r="K10" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="L10" s="38"/>
+      <c r="M10" s="39"/>
       <c r="N10" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="O10" s="54" t="s">
-        <v>109</v>
-      </c>
-      <c r="P10" s="55"/>
-      <c r="Q10" s="55"/>
-      <c r="R10" s="55"/>
-      <c r="S10" s="55"/>
-      <c r="T10" s="55"/>
-      <c r="U10" s="56"/>
+      <c r="O10" s="77" t="s">
+        <v>104</v>
+      </c>
+      <c r="P10" s="78"/>
+      <c r="Q10" s="78"/>
+      <c r="R10" s="78"/>
+      <c r="S10" s="78"/>
+      <c r="T10" s="78"/>
+      <c r="U10" s="79"/>
       <c r="V10" s="35"/>
       <c r="W10" s="36"/>
       <c r="X10" s="35"/>
-      <c r="Y10" s="57"/>
-      <c r="Z10" s="58"/>
+      <c r="Y10" s="46"/>
+      <c r="Z10" s="47"/>
     </row>
     <row r="11" spans="1:29" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A11" s="105"/>
-      <c r="B11" s="106"/>
-      <c r="C11" s="107"/>
+      <c r="A11" s="117"/>
+      <c r="B11" s="118"/>
+      <c r="C11" s="119"/>
       <c r="D11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="54" t="s">
-        <v>119</v>
-      </c>
-      <c r="F11" s="56"/>
+      <c r="E11" s="77" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11" s="79"/>
       <c r="G11" s="21"/>
       <c r="H11" s="22"/>
       <c r="I11" s="21"/>
-      <c r="J11" s="52"/>
+      <c r="J11" s="100"/>
       <c r="K11" s="23"/>
       <c r="L11" s="24"/>
       <c r="M11" s="25"/>
       <c r="N11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="O11" s="54" t="s">
-        <v>110</v>
-      </c>
-      <c r="P11" s="55"/>
-      <c r="Q11" s="55"/>
-      <c r="R11" s="55"/>
-      <c r="S11" s="55"/>
-      <c r="T11" s="55"/>
-      <c r="U11" s="56"/>
+      <c r="O11" s="77" t="s">
+        <v>105</v>
+      </c>
+      <c r="P11" s="78"/>
+      <c r="Q11" s="78"/>
+      <c r="R11" s="78"/>
+      <c r="S11" s="78"/>
+      <c r="T11" s="78"/>
+      <c r="U11" s="79"/>
       <c r="V11" s="33"/>
       <c r="W11" s="34"/>
       <c r="X11" s="33"/>
-      <c r="Y11" s="57"/>
-      <c r="Z11" s="58"/>
+      <c r="Y11" s="46"/>
+      <c r="Z11" s="47"/>
       <c r="AC11"/>
     </row>
     <row r="12" spans="1:29" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A12" s="108"/>
-      <c r="B12" s="109"/>
-      <c r="C12" s="110"/>
+      <c r="A12" s="120"/>
+      <c r="B12" s="121"/>
+      <c r="C12" s="122"/>
       <c r="D12" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="54" t="s">
-        <v>120</v>
-      </c>
-      <c r="F12" s="56"/>
+        <v>39</v>
+      </c>
+      <c r="E12" s="77" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12" s="79"/>
       <c r="G12" s="21"/>
       <c r="H12" s="22"/>
       <c r="I12" s="21"/>
-      <c r="J12" s="52"/>
+      <c r="J12" s="100"/>
       <c r="K12" s="23"/>
       <c r="L12" s="24"/>
       <c r="M12" s="25"/>
       <c r="N12" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="O12" s="64" t="s">
-        <v>133</v>
-      </c>
-      <c r="P12" s="55"/>
-      <c r="Q12" s="55"/>
-      <c r="R12" s="55"/>
-      <c r="S12" s="55"/>
-      <c r="T12" s="55"/>
-      <c r="U12" s="56"/>
+        <v>39</v>
+      </c>
+      <c r="O12" s="88" t="s">
+        <v>128</v>
+      </c>
+      <c r="P12" s="78"/>
+      <c r="Q12" s="78"/>
+      <c r="R12" s="78"/>
+      <c r="S12" s="78"/>
+      <c r="T12" s="78"/>
+      <c r="U12" s="79"/>
       <c r="V12" s="33"/>
       <c r="W12" s="34"/>
       <c r="X12" s="33"/>
-      <c r="Y12" s="57"/>
-      <c r="Z12" s="58"/>
+      <c r="Y12" s="46"/>
+      <c r="Z12" s="47"/>
     </row>
     <row r="13" spans="1:29" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A13" s="108"/>
-      <c r="B13" s="109"/>
-      <c r="C13" s="110"/>
+      <c r="A13" s="120"/>
+      <c r="B13" s="121"/>
+      <c r="C13" s="122"/>
       <c r="D13" s="15">
         <v>2</v>
       </c>
-      <c r="E13" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="48"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="67"/>
-      <c r="J13" s="52"/>
+      <c r="E13" s="84" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="85"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="100"/>
       <c r="K13" s="23"/>
       <c r="L13" s="24"/>
       <c r="M13" s="25"/>
       <c r="N13" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="O13" s="54" t="s">
-        <v>89</v>
-      </c>
-      <c r="P13" s="55"/>
-      <c r="Q13" s="55"/>
-      <c r="R13" s="55"/>
-      <c r="S13" s="55"/>
-      <c r="T13" s="55"/>
-      <c r="U13" s="56"/>
+        <v>40</v>
+      </c>
+      <c r="O13" s="77" t="s">
+        <v>86</v>
+      </c>
+      <c r="P13" s="78"/>
+      <c r="Q13" s="78"/>
+      <c r="R13" s="78"/>
+      <c r="S13" s="78"/>
+      <c r="T13" s="78"/>
+      <c r="U13" s="79"/>
       <c r="V13" s="33"/>
       <c r="W13" s="34"/>
       <c r="X13" s="33"/>
-      <c r="Y13" s="57"/>
-      <c r="Z13" s="58"/>
+      <c r="Y13" s="46"/>
+      <c r="Z13" s="47"/>
     </row>
     <row r="14" spans="1:29" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A14" s="108"/>
-      <c r="B14" s="109"/>
-      <c r="C14" s="110"/>
+      <c r="A14" s="120"/>
+      <c r="B14" s="121"/>
+      <c r="C14" s="122"/>
       <c r="D14" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E14" s="54" t="s">
-        <v>121</v>
-      </c>
-      <c r="F14" s="56"/>
+      <c r="E14" s="77" t="s">
+        <v>116</v>
+      </c>
+      <c r="F14" s="79"/>
       <c r="G14" s="21"/>
       <c r="H14" s="22"/>
       <c r="I14" s="21"/>
-      <c r="J14" s="52"/>
+      <c r="J14" s="100"/>
       <c r="K14" s="23"/>
       <c r="L14" s="24"/>
       <c r="M14" s="25"/>
       <c r="N14" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="O14" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="P14" s="55"/>
-      <c r="Q14" s="55"/>
-      <c r="R14" s="55"/>
-      <c r="S14" s="55"/>
-      <c r="T14" s="55"/>
-      <c r="U14" s="56"/>
+        <v>41</v>
+      </c>
+      <c r="O14" s="77" t="s">
+        <v>106</v>
+      </c>
+      <c r="P14" s="78"/>
+      <c r="Q14" s="78"/>
+      <c r="R14" s="78"/>
+      <c r="S14" s="78"/>
+      <c r="T14" s="78"/>
+      <c r="U14" s="79"/>
       <c r="V14" s="33"/>
       <c r="W14" s="34"/>
       <c r="X14" s="33"/>
-      <c r="Y14" s="57"/>
-      <c r="Z14" s="58"/>
+      <c r="Y14" s="46"/>
+      <c r="Z14" s="47"/>
     </row>
     <row r="15" spans="1:29" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A15" s="108"/>
-      <c r="B15" s="109"/>
-      <c r="C15" s="110"/>
+      <c r="A15" s="120"/>
+      <c r="B15" s="121"/>
+      <c r="C15" s="122"/>
       <c r="D15" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="54" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="56"/>
+      <c r="E15" s="77" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="79"/>
       <c r="G15" s="21"/>
       <c r="H15" s="22"/>
       <c r="I15" s="21"/>
-      <c r="J15" s="52"/>
+      <c r="J15" s="100"/>
       <c r="K15" s="23"/>
       <c r="L15" s="24"/>
       <c r="M15" s="25"/>
       <c r="N15" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="O15" s="54" t="s">
-        <v>112</v>
-      </c>
-      <c r="P15" s="55"/>
-      <c r="Q15" s="55"/>
-      <c r="R15" s="55"/>
-      <c r="S15" s="55"/>
-      <c r="T15" s="55"/>
-      <c r="U15" s="56"/>
+        <v>42</v>
+      </c>
+      <c r="O15" s="77" t="s">
+        <v>107</v>
+      </c>
+      <c r="P15" s="78"/>
+      <c r="Q15" s="78"/>
+      <c r="R15" s="78"/>
+      <c r="S15" s="78"/>
+      <c r="T15" s="78"/>
+      <c r="U15" s="79"/>
       <c r="V15" s="33"/>
       <c r="W15" s="34"/>
       <c r="X15" s="33"/>
-      <c r="Y15" s="57"/>
-      <c r="Z15" s="58"/>
+      <c r="Y15" s="46"/>
+      <c r="Z15" s="47"/>
       <c r="AA15" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:29" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A16" s="108"/>
-      <c r="B16" s="109"/>
-      <c r="C16" s="110"/>
+      <c r="A16" s="120"/>
+      <c r="B16" s="121"/>
+      <c r="C16" s="122"/>
       <c r="D16" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="54" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="56"/>
+        <v>45</v>
+      </c>
+      <c r="E16" s="77" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="79"/>
       <c r="G16" s="21"/>
       <c r="H16" s="22"/>
       <c r="I16" s="21"/>
-      <c r="J16" s="52"/>
+      <c r="J16" s="100"/>
       <c r="K16" s="23"/>
       <c r="L16" s="24"/>
       <c r="M16" s="25"/>
       <c r="N16" s="15">
         <v>2</v>
       </c>
-      <c r="O16" s="46" t="s">
-        <v>156</v>
-      </c>
-      <c r="P16" s="47"/>
-      <c r="Q16" s="47"/>
-      <c r="R16" s="47"/>
-      <c r="S16" s="47"/>
-      <c r="T16" s="47"/>
-      <c r="U16" s="48"/>
+      <c r="O16" s="84" t="s">
+        <v>151</v>
+      </c>
+      <c r="P16" s="87"/>
+      <c r="Q16" s="87"/>
+      <c r="R16" s="87"/>
+      <c r="S16" s="87"/>
+      <c r="T16" s="87"/>
+      <c r="U16" s="85"/>
       <c r="V16" s="114"/>
       <c r="W16" s="115"/>
       <c r="X16" s="116"/>
-      <c r="Y16" s="57"/>
-      <c r="Z16" s="58"/>
+      <c r="Y16" s="46"/>
+      <c r="Z16" s="47"/>
     </row>
     <row r="17" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A17" s="108"/>
-      <c r="B17" s="109"/>
-      <c r="C17" s="110"/>
+      <c r="A17" s="120"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="122"/>
       <c r="D17" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="54" t="s">
-        <v>122</v>
-      </c>
-      <c r="F17" s="56"/>
+        <v>46</v>
+      </c>
+      <c r="E17" s="77" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17" s="79"/>
       <c r="G17" s="20"/>
       <c r="H17" s="28"/>
       <c r="I17" s="20"/>
-      <c r="J17" s="52"/>
+      <c r="J17" s="100"/>
       <c r="K17" s="23"/>
       <c r="L17" s="24"/>
       <c r="M17" s="25"/>
       <c r="N17" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="O17" s="54" t="s">
-        <v>61</v>
-      </c>
-      <c r="P17" s="55"/>
-      <c r="Q17" s="55"/>
-      <c r="R17" s="55"/>
-      <c r="S17" s="55"/>
-      <c r="T17" s="55"/>
-      <c r="U17" s="56"/>
+      <c r="O17" s="77" t="s">
+        <v>58</v>
+      </c>
+      <c r="P17" s="78"/>
+      <c r="Q17" s="78"/>
+      <c r="R17" s="78"/>
+      <c r="S17" s="78"/>
+      <c r="T17" s="78"/>
+      <c r="U17" s="79"/>
       <c r="V17" s="20"/>
       <c r="W17" s="28"/>
       <c r="X17" s="20"/>
-      <c r="Y17" s="57"/>
-      <c r="Z17" s="58"/>
+      <c r="Y17" s="46"/>
+      <c r="Z17" s="47"/>
     </row>
     <row r="18" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A18" s="108"/>
-      <c r="B18" s="109"/>
-      <c r="C18" s="110"/>
+      <c r="A18" s="120"/>
+      <c r="B18" s="121"/>
+      <c r="C18" s="122"/>
       <c r="D18" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" s="54" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" s="56"/>
+        <v>52</v>
+      </c>
+      <c r="E18" s="77" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="79"/>
       <c r="G18" s="7"/>
       <c r="H18" s="3"/>
       <c r="I18" s="7"/>
-      <c r="J18" s="52"/>
+      <c r="J18" s="100"/>
       <c r="K18" s="23"/>
       <c r="L18" s="24"/>
       <c r="M18" s="25"/>
       <c r="N18" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="O18" s="54" t="s">
-        <v>113</v>
-      </c>
-      <c r="P18" s="55"/>
-      <c r="Q18" s="55"/>
-      <c r="R18" s="55"/>
-      <c r="S18" s="55"/>
-      <c r="T18" s="55"/>
-      <c r="U18" s="56"/>
+      <c r="O18" s="77" t="s">
+        <v>108</v>
+      </c>
+      <c r="P18" s="78"/>
+      <c r="Q18" s="78"/>
+      <c r="R18" s="78"/>
+      <c r="S18" s="78"/>
+      <c r="T18" s="78"/>
+      <c r="U18" s="79"/>
       <c r="V18" s="33"/>
       <c r="W18" s="34"/>
       <c r="X18" s="33"/>
-      <c r="Y18" s="57"/>
-      <c r="Z18" s="58"/>
+      <c r="Y18" s="46"/>
+      <c r="Z18" s="47"/>
     </row>
     <row r="19" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A19" s="108"/>
-      <c r="B19" s="109"/>
-      <c r="C19" s="110"/>
+      <c r="A19" s="120"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="122"/>
       <c r="D19" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E19" s="54" t="s">
-        <v>73</v>
-      </c>
-      <c r="F19" s="56"/>
+        <v>53</v>
+      </c>
+      <c r="E19" s="77" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="79"/>
       <c r="G19" s="20"/>
       <c r="H19" s="28"/>
       <c r="I19" s="20"/>
-      <c r="J19" s="52"/>
+      <c r="J19" s="100"/>
       <c r="K19" s="23"/>
       <c r="L19" s="24"/>
       <c r="M19" s="25"/>
       <c r="N19" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="O19" s="54" t="s">
-        <v>114</v>
-      </c>
-      <c r="P19" s="55"/>
-      <c r="Q19" s="55"/>
-      <c r="R19" s="55"/>
-      <c r="S19" s="55"/>
-      <c r="T19" s="55"/>
-      <c r="U19" s="56"/>
+        <v>45</v>
+      </c>
+      <c r="O19" s="77" t="s">
+        <v>109</v>
+      </c>
+      <c r="P19" s="78"/>
+      <c r="Q19" s="78"/>
+      <c r="R19" s="78"/>
+      <c r="S19" s="78"/>
+      <c r="T19" s="78"/>
+      <c r="U19" s="79"/>
       <c r="V19" s="20"/>
       <c r="W19" s="28"/>
       <c r="X19" s="20"/>
-      <c r="Y19" s="57"/>
-      <c r="Z19" s="58"/>
+      <c r="Y19" s="46"/>
+      <c r="Z19" s="47"/>
     </row>
     <row r="20" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A20" s="108"/>
-      <c r="B20" s="109"/>
-      <c r="C20" s="110"/>
+      <c r="A20" s="120"/>
+      <c r="B20" s="121"/>
+      <c r="C20" s="122"/>
       <c r="D20" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="54" t="s">
-        <v>123</v>
-      </c>
-      <c r="F20" s="56"/>
+        <v>54</v>
+      </c>
+      <c r="E20" s="77" t="s">
+        <v>118</v>
+      </c>
+      <c r="F20" s="79"/>
       <c r="G20" s="7"/>
       <c r="H20" s="3"/>
       <c r="I20" s="7"/>
-      <c r="J20" s="52"/>
+      <c r="J20" s="100"/>
       <c r="K20" s="23"/>
       <c r="L20" s="24"/>
       <c r="M20" s="25"/>
       <c r="N20" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="O20" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="P20" s="55"/>
-      <c r="Q20" s="55"/>
-      <c r="R20" s="55"/>
-      <c r="S20" s="55"/>
-      <c r="T20" s="55"/>
-      <c r="U20" s="56"/>
+        <v>46</v>
+      </c>
+      <c r="O20" s="77" t="s">
+        <v>57</v>
+      </c>
+      <c r="P20" s="78"/>
+      <c r="Q20" s="78"/>
+      <c r="R20" s="78"/>
+      <c r="S20" s="78"/>
+      <c r="T20" s="78"/>
+      <c r="U20" s="79"/>
       <c r="V20" s="33"/>
       <c r="W20" s="34"/>
       <c r="X20" s="33"/>
-      <c r="Y20" s="57"/>
-      <c r="Z20" s="58"/>
+      <c r="Y20" s="46"/>
+      <c r="Z20" s="47"/>
     </row>
     <row r="21" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A21" s="108"/>
-      <c r="B21" s="109"/>
-      <c r="C21" s="110"/>
+      <c r="A21" s="120"/>
+      <c r="B21" s="121"/>
+      <c r="C21" s="122"/>
       <c r="D21" s="15">
         <v>3</v>
       </c>
-      <c r="E21" s="46" t="s">
-        <v>92</v>
-      </c>
-      <c r="F21" s="48"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="66"/>
-      <c r="I21" s="67"/>
-      <c r="J21" s="52"/>
+      <c r="E21" s="84" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" s="85"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="100"/>
       <c r="K21" s="23"/>
       <c r="L21" s="24"/>
       <c r="M21" s="25"/>
       <c r="N21" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="O21" s="54" t="s">
-        <v>115</v>
-      </c>
-      <c r="P21" s="55"/>
-      <c r="Q21" s="55"/>
-      <c r="R21" s="55"/>
-      <c r="S21" s="55"/>
-      <c r="T21" s="55"/>
-      <c r="U21" s="56"/>
+        <v>52</v>
+      </c>
+      <c r="O21" s="77" t="s">
+        <v>110</v>
+      </c>
+      <c r="P21" s="78"/>
+      <c r="Q21" s="78"/>
+      <c r="R21" s="78"/>
+      <c r="S21" s="78"/>
+      <c r="T21" s="78"/>
+      <c r="U21" s="79"/>
       <c r="V21" s="33"/>
       <c r="W21" s="34"/>
       <c r="X21" s="33"/>
-      <c r="Y21" s="57"/>
-      <c r="Z21" s="58"/>
+      <c r="Y21" s="46"/>
+      <c r="Z21" s="47"/>
     </row>
     <row r="22" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A22" s="108"/>
-      <c r="B22" s="109"/>
-      <c r="C22" s="110"/>
+      <c r="A22" s="120"/>
+      <c r="B22" s="121"/>
+      <c r="C22" s="122"/>
       <c r="D22" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="54" t="s">
-        <v>124</v>
-      </c>
-      <c r="F22" s="56"/>
+      <c r="E22" s="77" t="s">
+        <v>119</v>
+      </c>
+      <c r="F22" s="79"/>
       <c r="G22" s="20"/>
       <c r="H22" s="28"/>
       <c r="I22" s="20"/>
-      <c r="J22" s="52"/>
+      <c r="J22" s="100"/>
       <c r="K22" s="23"/>
       <c r="L22" s="24"/>
       <c r="M22" s="25"/>
       <c r="N22" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="O22" s="54" t="s">
-        <v>116</v>
-      </c>
-      <c r="P22" s="55"/>
-      <c r="Q22" s="55"/>
-      <c r="R22" s="55"/>
-      <c r="S22" s="55"/>
-      <c r="T22" s="55"/>
-      <c r="U22" s="56"/>
+        <v>53</v>
+      </c>
+      <c r="O22" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="P22" s="78"/>
+      <c r="Q22" s="78"/>
+      <c r="R22" s="78"/>
+      <c r="S22" s="78"/>
+      <c r="T22" s="78"/>
+      <c r="U22" s="79"/>
       <c r="V22" s="20"/>
       <c r="W22" s="28"/>
       <c r="X22" s="20"/>
-      <c r="Y22" s="57"/>
-      <c r="Z22" s="58"/>
+      <c r="Y22" s="46"/>
+      <c r="Z22" s="47"/>
     </row>
     <row r="23" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A23" s="108"/>
-      <c r="B23" s="109"/>
-      <c r="C23" s="110"/>
+      <c r="A23" s="120"/>
+      <c r="B23" s="121"/>
+      <c r="C23" s="122"/>
       <c r="D23" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="54" t="s">
-        <v>35</v>
-      </c>
-      <c r="F23" s="56"/>
+      <c r="E23" s="77" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" s="79"/>
       <c r="G23" s="7"/>
       <c r="H23" s="3"/>
       <c r="I23" s="7"/>
-      <c r="J23" s="52"/>
+      <c r="J23" s="100"/>
       <c r="K23" s="23"/>
       <c r="L23" s="24"/>
       <c r="M23" s="25"/>
       <c r="N23" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="O23" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="P23" s="55"/>
-      <c r="Q23" s="55"/>
-      <c r="R23" s="55"/>
-      <c r="S23" s="55"/>
-      <c r="T23" s="55"/>
-      <c r="U23" s="56"/>
+        <v>54</v>
+      </c>
+      <c r="O23" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="P23" s="78"/>
+      <c r="Q23" s="78"/>
+      <c r="R23" s="78"/>
+      <c r="S23" s="78"/>
+      <c r="T23" s="78"/>
+      <c r="U23" s="79"/>
       <c r="V23" s="33"/>
       <c r="W23" s="34"/>
       <c r="X23" s="33"/>
-      <c r="Y23" s="57"/>
-      <c r="Z23" s="58"/>
+      <c r="Y23" s="46"/>
+      <c r="Z23" s="47"/>
     </row>
     <row r="24" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A24" s="108"/>
-      <c r="B24" s="109"/>
-      <c r="C24" s="110"/>
+      <c r="A24" s="120"/>
+      <c r="B24" s="121"/>
+      <c r="C24" s="122"/>
       <c r="D24" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="E24" s="54" t="s">
-        <v>125</v>
-      </c>
-      <c r="F24" s="56"/>
+        <v>47</v>
+      </c>
+      <c r="E24" s="77" t="s">
+        <v>120</v>
+      </c>
+      <c r="F24" s="79"/>
       <c r="G24" s="7"/>
       <c r="H24" s="3"/>
       <c r="I24" s="7"/>
-      <c r="J24" s="52"/>
+      <c r="J24" s="100"/>
       <c r="K24" s="23"/>
       <c r="L24" s="24"/>
       <c r="M24" s="25"/>
       <c r="N24" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="O24" s="54" t="s">
-        <v>63</v>
-      </c>
-      <c r="P24" s="55"/>
-      <c r="Q24" s="55"/>
-      <c r="R24" s="55"/>
-      <c r="S24" s="55"/>
-      <c r="T24" s="55"/>
-      <c r="U24" s="56"/>
+        <v>74</v>
+      </c>
+      <c r="O24" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="P24" s="78"/>
+      <c r="Q24" s="78"/>
+      <c r="R24" s="78"/>
+      <c r="S24" s="78"/>
+      <c r="T24" s="78"/>
+      <c r="U24" s="79"/>
       <c r="V24" s="33"/>
       <c r="W24" s="34"/>
       <c r="X24" s="33"/>
-      <c r="Y24" s="57"/>
-      <c r="Z24" s="58"/>
+      <c r="Y24" s="46"/>
+      <c r="Z24" s="47"/>
     </row>
     <row r="25" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A25" s="108"/>
-      <c r="B25" s="109"/>
-      <c r="C25" s="110"/>
+      <c r="A25" s="120"/>
+      <c r="B25" s="121"/>
+      <c r="C25" s="122"/>
       <c r="D25" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="54" t="s">
-        <v>126</v>
-      </c>
-      <c r="F25" s="56"/>
+      <c r="E25" s="77" t="s">
+        <v>121</v>
+      </c>
+      <c r="F25" s="79"/>
       <c r="G25" s="7"/>
       <c r="H25" s="3"/>
       <c r="I25" s="7"/>
-      <c r="J25" s="52"/>
+      <c r="J25" s="100"/>
       <c r="K25" s="23"/>
       <c r="L25" s="24"/>
       <c r="M25" s="25"/>
       <c r="N25" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="O25" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="P25" s="55"/>
-      <c r="Q25" s="55"/>
-      <c r="R25" s="55"/>
-      <c r="S25" s="55"/>
-      <c r="T25" s="55"/>
-      <c r="U25" s="56"/>
+        <v>75</v>
+      </c>
+      <c r="O25" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="P25" s="78"/>
+      <c r="Q25" s="78"/>
+      <c r="R25" s="78"/>
+      <c r="S25" s="78"/>
+      <c r="T25" s="78"/>
+      <c r="U25" s="79"/>
       <c r="V25" s="33"/>
       <c r="W25" s="34"/>
       <c r="X25" s="33"/>
-      <c r="Y25" s="57"/>
-      <c r="Z25" s="58"/>
+      <c r="Y25" s="46"/>
+      <c r="Z25" s="47"/>
     </row>
     <row r="26" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A26" s="108"/>
-      <c r="B26" s="109"/>
-      <c r="C26" s="110"/>
+      <c r="A26" s="120"/>
+      <c r="B26" s="121"/>
+      <c r="C26" s="122"/>
       <c r="D26" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="F26" s="56"/>
+      <c r="E26" s="77" t="s">
+        <v>122</v>
+      </c>
+      <c r="F26" s="79"/>
       <c r="G26" s="7"/>
       <c r="H26" s="3"/>
       <c r="I26" s="7"/>
-      <c r="J26" s="52"/>
+      <c r="J26" s="100"/>
       <c r="K26" s="23"/>
       <c r="L26" s="24"/>
       <c r="M26" s="25"/>
       <c r="N26" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="O26" s="54" t="s">
-        <v>117</v>
-      </c>
-      <c r="P26" s="55"/>
-      <c r="Q26" s="55"/>
-      <c r="R26" s="55"/>
-      <c r="S26" s="55"/>
-      <c r="T26" s="55"/>
-      <c r="U26" s="56"/>
+        <v>76</v>
+      </c>
+      <c r="O26" s="77" t="s">
+        <v>112</v>
+      </c>
+      <c r="P26" s="78"/>
+      <c r="Q26" s="78"/>
+      <c r="R26" s="78"/>
+      <c r="S26" s="78"/>
+      <c r="T26" s="78"/>
+      <c r="U26" s="79"/>
       <c r="V26" s="33"/>
       <c r="W26" s="34"/>
       <c r="X26" s="33"/>
-      <c r="Y26" s="57"/>
-      <c r="Z26" s="58"/>
+      <c r="Y26" s="46"/>
+      <c r="Z26" s="47"/>
     </row>
     <row r="27" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A27" s="108"/>
-      <c r="B27" s="109"/>
-      <c r="C27" s="110"/>
+      <c r="A27" s="120"/>
+      <c r="B27" s="121"/>
+      <c r="C27" s="122"/>
       <c r="D27" s="15">
         <v>4</v>
       </c>
-      <c r="E27" s="46" t="s">
-        <v>102</v>
-      </c>
-      <c r="F27" s="48"/>
-      <c r="G27" s="65"/>
-      <c r="H27" s="66"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="52"/>
+      <c r="E27" s="84" t="s">
+        <v>99</v>
+      </c>
+      <c r="F27" s="85"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="100"/>
       <c r="K27" s="23"/>
       <c r="L27" s="24"/>
       <c r="M27" s="25"/>
       <c r="N27" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="O27" s="77" t="s">
         <v>80</v>
       </c>
-      <c r="O27" s="54" t="s">
-        <v>83</v>
-      </c>
-      <c r="P27" s="55"/>
-      <c r="Q27" s="55"/>
-      <c r="R27" s="55"/>
-      <c r="S27" s="55"/>
-      <c r="T27" s="55"/>
-      <c r="U27" s="56"/>
+      <c r="P27" s="78"/>
+      <c r="Q27" s="78"/>
+      <c r="R27" s="78"/>
+      <c r="S27" s="78"/>
+      <c r="T27" s="78"/>
+      <c r="U27" s="79"/>
       <c r="V27" s="33"/>
       <c r="W27" s="34"/>
       <c r="X27" s="33"/>
-      <c r="Y27" s="57"/>
-      <c r="Z27" s="58"/>
+      <c r="Y27" s="46"/>
+      <c r="Z27" s="47"/>
     </row>
     <row r="28" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A28" s="108"/>
-      <c r="B28" s="109"/>
-      <c r="C28" s="110"/>
+      <c r="A28" s="120"/>
+      <c r="B28" s="121"/>
+      <c r="C28" s="122"/>
       <c r="D28" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="54" t="s">
-        <v>65</v>
-      </c>
-      <c r="F28" s="56"/>
+      <c r="E28" s="77" t="s">
+        <v>62</v>
+      </c>
+      <c r="F28" s="79"/>
       <c r="G28" s="7"/>
       <c r="H28" s="3"/>
       <c r="I28" s="7"/>
-      <c r="J28" s="52"/>
+      <c r="J28" s="100"/>
       <c r="K28" s="23"/>
       <c r="L28" s="24"/>
       <c r="M28" s="25"/>
       <c r="N28" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="O28" s="77" t="s">
         <v>81</v>
       </c>
-      <c r="O28" s="54" t="s">
-        <v>84</v>
-      </c>
-      <c r="P28" s="55"/>
-      <c r="Q28" s="55"/>
-      <c r="R28" s="55"/>
-      <c r="S28" s="55"/>
-      <c r="T28" s="55"/>
-      <c r="U28" s="56"/>
+      <c r="P28" s="78"/>
+      <c r="Q28" s="78"/>
+      <c r="R28" s="78"/>
+      <c r="S28" s="78"/>
+      <c r="T28" s="78"/>
+      <c r="U28" s="79"/>
       <c r="V28" s="33"/>
       <c r="W28" s="34"/>
       <c r="X28" s="33"/>
-      <c r="Y28" s="57"/>
-      <c r="Z28" s="58"/>
+      <c r="Y28" s="46"/>
+      <c r="Z28" s="47"/>
     </row>
     <row r="29" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A29" s="108"/>
-      <c r="B29" s="109"/>
-      <c r="C29" s="110"/>
+      <c r="A29" s="120"/>
+      <c r="B29" s="121"/>
+      <c r="C29" s="122"/>
       <c r="D29" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="54" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" s="56"/>
+      <c r="E29" s="77" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29" s="79"/>
       <c r="G29" s="7"/>
       <c r="H29" s="3"/>
       <c r="I29" s="7"/>
-      <c r="J29" s="52"/>
+      <c r="J29" s="100"/>
       <c r="K29" s="23"/>
       <c r="L29" s="24"/>
       <c r="M29" s="25"/>
       <c r="N29" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="O29" s="54" t="s">
-        <v>62</v>
-      </c>
-      <c r="P29" s="55"/>
-      <c r="Q29" s="55"/>
-      <c r="R29" s="55"/>
-      <c r="S29" s="55"/>
-      <c r="T29" s="55"/>
-      <c r="U29" s="56"/>
+        <v>79</v>
+      </c>
+      <c r="O29" s="77" t="s">
+        <v>59</v>
+      </c>
+      <c r="P29" s="78"/>
+      <c r="Q29" s="78"/>
+      <c r="R29" s="78"/>
+      <c r="S29" s="78"/>
+      <c r="T29" s="78"/>
+      <c r="U29" s="79"/>
       <c r="V29" s="33"/>
       <c r="W29" s="34"/>
       <c r="X29" s="33"/>
-      <c r="Y29" s="57"/>
-      <c r="Z29" s="58"/>
+      <c r="Y29" s="46"/>
+      <c r="Z29" s="47"/>
     </row>
     <row r="30" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A30" s="108"/>
-      <c r="B30" s="109"/>
-      <c r="C30" s="110"/>
+      <c r="A30" s="120"/>
+      <c r="B30" s="121"/>
+      <c r="C30" s="122"/>
       <c r="D30" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E30" s="54" t="s">
-        <v>128</v>
-      </c>
-      <c r="F30" s="56"/>
+        <v>49</v>
+      </c>
+      <c r="E30" s="77" t="s">
+        <v>123</v>
+      </c>
+      <c r="F30" s="79"/>
       <c r="G30" s="20"/>
       <c r="H30" s="3"/>
       <c r="I30" s="20"/>
-      <c r="J30" s="52"/>
+      <c r="J30" s="100"/>
       <c r="K30" s="23"/>
       <c r="L30" s="24"/>
       <c r="M30" s="25"/>
-      <c r="N30" s="117"/>
-      <c r="O30" s="118"/>
-      <c r="P30" s="118"/>
-      <c r="Q30" s="118"/>
-      <c r="R30" s="118"/>
-      <c r="S30" s="118"/>
-      <c r="T30" s="118"/>
-      <c r="U30" s="118"/>
-      <c r="V30" s="118"/>
-      <c r="W30" s="118"/>
-      <c r="X30" s="118"/>
-      <c r="Y30" s="118"/>
-      <c r="Z30" s="119"/>
+      <c r="N30" s="105"/>
+      <c r="O30" s="106"/>
+      <c r="P30" s="106"/>
+      <c r="Q30" s="106"/>
+      <c r="R30" s="106"/>
+      <c r="S30" s="106"/>
+      <c r="T30" s="106"/>
+      <c r="U30" s="106"/>
+      <c r="V30" s="106"/>
+      <c r="W30" s="106"/>
+      <c r="X30" s="106"/>
+      <c r="Y30" s="106"/>
+      <c r="Z30" s="107"/>
     </row>
     <row r="31" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A31" s="108"/>
-      <c r="B31" s="109"/>
-      <c r="C31" s="110"/>
+      <c r="A31" s="120"/>
+      <c r="B31" s="121"/>
+      <c r="C31" s="122"/>
       <c r="D31" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E31" s="54" t="s">
-        <v>36</v>
-      </c>
-      <c r="F31" s="56"/>
+        <v>50</v>
+      </c>
+      <c r="E31" s="77" t="s">
+        <v>34</v>
+      </c>
+      <c r="F31" s="79"/>
       <c r="G31" s="20"/>
       <c r="H31" s="3"/>
       <c r="I31" s="20"/>
-      <c r="J31" s="52"/>
+      <c r="J31" s="100"/>
       <c r="K31" s="23"/>
       <c r="L31" s="24"/>
       <c r="M31" s="25"/>
-      <c r="N31" s="120"/>
-      <c r="O31" s="121"/>
-      <c r="P31" s="121"/>
-      <c r="Q31" s="121"/>
-      <c r="R31" s="121"/>
-      <c r="S31" s="121"/>
-      <c r="T31" s="121"/>
-      <c r="U31" s="121"/>
-      <c r="V31" s="121"/>
-      <c r="W31" s="121"/>
-      <c r="X31" s="121"/>
-      <c r="Y31" s="121"/>
-      <c r="Z31" s="122"/>
+      <c r="N31" s="108"/>
+      <c r="O31" s="109"/>
+      <c r="P31" s="109"/>
+      <c r="Q31" s="109"/>
+      <c r="R31" s="109"/>
+      <c r="S31" s="109"/>
+      <c r="T31" s="109"/>
+      <c r="U31" s="109"/>
+      <c r="V31" s="109"/>
+      <c r="W31" s="109"/>
+      <c r="X31" s="109"/>
+      <c r="Y31" s="109"/>
+      <c r="Z31" s="110"/>
     </row>
     <row r="32" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A32" s="108"/>
-      <c r="B32" s="109"/>
-      <c r="C32" s="110"/>
+      <c r="A32" s="120"/>
+      <c r="B32" s="121"/>
+      <c r="C32" s="122"/>
       <c r="D32" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E32" s="54" t="s">
-        <v>129</v>
-      </c>
-      <c r="F32" s="56"/>
+        <v>51</v>
+      </c>
+      <c r="E32" s="77" t="s">
+        <v>124</v>
+      </c>
+      <c r="F32" s="79"/>
       <c r="G32" s="20"/>
       <c r="H32" s="3"/>
       <c r="I32" s="20"/>
-      <c r="J32" s="52"/>
+      <c r="J32" s="100"/>
       <c r="K32" s="23"/>
       <c r="L32" s="24"/>
       <c r="M32" s="25"/>
-      <c r="N32" s="120"/>
-      <c r="O32" s="121"/>
-      <c r="P32" s="121"/>
-      <c r="Q32" s="121"/>
-      <c r="R32" s="121"/>
-      <c r="S32" s="121"/>
-      <c r="T32" s="121"/>
-      <c r="U32" s="121"/>
-      <c r="V32" s="121"/>
-      <c r="W32" s="121"/>
-      <c r="X32" s="121"/>
-      <c r="Y32" s="121"/>
-      <c r="Z32" s="122"/>
+      <c r="N32" s="108"/>
+      <c r="O32" s="109"/>
+      <c r="P32" s="109"/>
+      <c r="Q32" s="109"/>
+      <c r="R32" s="109"/>
+      <c r="S32" s="109"/>
+      <c r="T32" s="109"/>
+      <c r="U32" s="109"/>
+      <c r="V32" s="109"/>
+      <c r="W32" s="109"/>
+      <c r="X32" s="109"/>
+      <c r="Y32" s="109"/>
+      <c r="Z32" s="110"/>
     </row>
     <row r="33" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A33" s="108"/>
-      <c r="B33" s="109"/>
-      <c r="C33" s="110"/>
+      <c r="A33" s="120"/>
+      <c r="B33" s="121"/>
+      <c r="C33" s="122"/>
       <c r="D33" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E33" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="F33" s="56"/>
+        <v>55</v>
+      </c>
+      <c r="E33" s="77" t="s">
+        <v>35</v>
+      </c>
+      <c r="F33" s="79"/>
       <c r="G33" s="20"/>
       <c r="H33" s="3"/>
       <c r="I33" s="20"/>
-      <c r="J33" s="52"/>
+      <c r="J33" s="100"/>
       <c r="K33" s="23"/>
       <c r="L33" s="24"/>
       <c r="M33" s="25"/>
-      <c r="N33" s="120"/>
-      <c r="O33" s="121"/>
-      <c r="P33" s="121"/>
-      <c r="Q33" s="121"/>
-      <c r="R33" s="121"/>
-      <c r="S33" s="121"/>
-      <c r="T33" s="121"/>
-      <c r="U33" s="121"/>
-      <c r="V33" s="121"/>
-      <c r="W33" s="121"/>
-      <c r="X33" s="121"/>
-      <c r="Y33" s="121"/>
-      <c r="Z33" s="122"/>
+      <c r="N33" s="108"/>
+      <c r="O33" s="109"/>
+      <c r="P33" s="109"/>
+      <c r="Q33" s="109"/>
+      <c r="R33" s="109"/>
+      <c r="S33" s="109"/>
+      <c r="T33" s="109"/>
+      <c r="U33" s="109"/>
+      <c r="V33" s="109"/>
+      <c r="W33" s="109"/>
+      <c r="X33" s="109"/>
+      <c r="Y33" s="109"/>
+      <c r="Z33" s="110"/>
     </row>
     <row r="34" spans="1:26" s="1" customFormat="1" ht="33.6" customHeight="1">
-      <c r="A34" s="111"/>
-      <c r="B34" s="112"/>
-      <c r="C34" s="113"/>
+      <c r="A34" s="123"/>
+      <c r="B34" s="124"/>
+      <c r="C34" s="125"/>
       <c r="D34" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E34" s="54" t="s">
-        <v>130</v>
-      </c>
-      <c r="F34" s="56"/>
+        <v>56</v>
+      </c>
+      <c r="E34" s="77" t="s">
+        <v>125</v>
+      </c>
+      <c r="F34" s="79"/>
       <c r="G34" s="20"/>
       <c r="H34" s="3"/>
       <c r="I34" s="20"/>
-      <c r="J34" s="52"/>
+      <c r="J34" s="100"/>
       <c r="K34" s="23"/>
       <c r="L34" s="24"/>
       <c r="M34" s="25"/>
-      <c r="N34" s="123"/>
-      <c r="O34" s="124"/>
-      <c r="P34" s="124"/>
-      <c r="Q34" s="124"/>
-      <c r="R34" s="124"/>
-      <c r="S34" s="124"/>
-      <c r="T34" s="124"/>
-      <c r="U34" s="124"/>
-      <c r="V34" s="124"/>
-      <c r="W34" s="124"/>
-      <c r="X34" s="124"/>
-      <c r="Y34" s="124"/>
-      <c r="Z34" s="125"/>
+      <c r="N34" s="111"/>
+      <c r="O34" s="112"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="112"/>
+      <c r="R34" s="112"/>
+      <c r="S34" s="112"/>
+      <c r="T34" s="112"/>
+      <c r="U34" s="112"/>
+      <c r="V34" s="112"/>
+      <c r="W34" s="112"/>
+      <c r="X34" s="112"/>
+      <c r="Y34" s="112"/>
+      <c r="Z34" s="113"/>
     </row>
     <row r="35" spans="1:26" s="1" customFormat="1" ht="7.5" customHeight="1">
-      <c r="A35" s="98"/>
-      <c r="B35" s="99"/>
-      <c r="C35" s="99"/>
-      <c r="D35" s="99"/>
-      <c r="E35" s="99"/>
-      <c r="F35" s="99"/>
-      <c r="G35" s="99"/>
-      <c r="H35" s="99"/>
-      <c r="I35" s="99"/>
-      <c r="J35" s="100"/>
-      <c r="K35" s="99"/>
-      <c r="L35" s="99"/>
-      <c r="M35" s="99"/>
-      <c r="N35" s="99"/>
-      <c r="O35" s="99"/>
-      <c r="P35" s="99"/>
-      <c r="Q35" s="99"/>
-      <c r="R35" s="99"/>
-      <c r="S35" s="99"/>
-      <c r="T35" s="99"/>
-      <c r="U35" s="99"/>
-      <c r="V35" s="99"/>
-      <c r="W35" s="99"/>
-      <c r="X35" s="99"/>
-      <c r="Y35" s="99"/>
-      <c r="Z35" s="101"/>
+      <c r="A35" s="61"/>
+      <c r="B35" s="62"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="62"/>
+      <c r="F35" s="62"/>
+      <c r="G35" s="62"/>
+      <c r="H35" s="62"/>
+      <c r="I35" s="62"/>
+      <c r="J35" s="63"/>
+      <c r="K35" s="62"/>
+      <c r="L35" s="62"/>
+      <c r="M35" s="62"/>
+      <c r="N35" s="62"/>
+      <c r="O35" s="62"/>
+      <c r="P35" s="62"/>
+      <c r="Q35" s="62"/>
+      <c r="R35" s="62"/>
+      <c r="S35" s="62"/>
+      <c r="T35" s="62"/>
+      <c r="U35" s="62"/>
+      <c r="V35" s="62"/>
+      <c r="W35" s="62"/>
+      <c r="X35" s="62"/>
+      <c r="Y35" s="62"/>
+      <c r="Z35" s="64"/>
     </row>
     <row r="36" spans="1:26" s="1" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A36" s="89" t="s">
-        <v>88</v>
-      </c>
-      <c r="B36" s="90"/>
-      <c r="C36" s="90"/>
-      <c r="D36" s="90"/>
-      <c r="E36" s="90"/>
-      <c r="F36" s="90"/>
-      <c r="G36" s="90"/>
-      <c r="H36" s="90"/>
-      <c r="I36" s="90"/>
-      <c r="J36" s="90"/>
-      <c r="K36" s="90"/>
-      <c r="L36" s="90"/>
-      <c r="M36" s="90"/>
-      <c r="N36" s="90"/>
-      <c r="O36" s="90"/>
-      <c r="P36" s="90"/>
-      <c r="Q36" s="90"/>
-      <c r="R36" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="S36" s="37"/>
-      <c r="T36" s="37"/>
-      <c r="U36" s="37"/>
-      <c r="V36" s="37"/>
-      <c r="W36" s="37"/>
+      <c r="A36" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
+      <c r="J36" s="51"/>
+      <c r="K36" s="51"/>
+      <c r="L36" s="51"/>
+      <c r="M36" s="51"/>
+      <c r="N36" s="51"/>
+      <c r="O36" s="51"/>
+      <c r="P36" s="51"/>
+      <c r="Q36" s="51"/>
+      <c r="R36" s="93" t="s">
+        <v>83</v>
+      </c>
+      <c r="S36" s="93"/>
+      <c r="T36" s="93"/>
+      <c r="U36" s="93"/>
+      <c r="V36" s="93"/>
+      <c r="W36" s="93"/>
       <c r="X36" s="29" t="s">
         <v>1</v>
       </c>
@@ -8387,35 +8384,35 @@
         <v>2</v>
       </c>
       <c r="Z36" s="31" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:26" s="1" customFormat="1" ht="29.4" customHeight="1">
-      <c r="A37" s="91"/>
-      <c r="B37" s="92"/>
-      <c r="C37" s="92"/>
-      <c r="D37" s="92"/>
-      <c r="E37" s="92"/>
-      <c r="F37" s="92"/>
-      <c r="G37" s="92"/>
-      <c r="H37" s="92"/>
-      <c r="I37" s="92"/>
-      <c r="J37" s="92"/>
-      <c r="K37" s="92"/>
-      <c r="L37" s="92"/>
-      <c r="M37" s="92"/>
-      <c r="N37" s="92"/>
-      <c r="O37" s="92"/>
-      <c r="P37" s="92"/>
-      <c r="Q37" s="92"/>
-      <c r="R37" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="S37" s="38"/>
-      <c r="T37" s="38"/>
-      <c r="U37" s="38"/>
-      <c r="V37" s="38"/>
-      <c r="W37" s="38"/>
+      <c r="A37" s="52"/>
+      <c r="B37" s="53"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="53"/>
+      <c r="N37" s="53"/>
+      <c r="O37" s="53"/>
+      <c r="P37" s="53"/>
+      <c r="Q37" s="53"/>
+      <c r="R37" s="94" t="s">
+        <v>88</v>
+      </c>
+      <c r="S37" s="94"/>
+      <c r="T37" s="94"/>
+      <c r="U37" s="94"/>
+      <c r="V37" s="94"/>
+      <c r="W37" s="94"/>
       <c r="X37" s="30" t="s">
         <v>1</v>
       </c>
@@ -8423,160 +8420,139 @@
         <v>2</v>
       </c>
       <c r="Z37" s="32" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:26" s="1" customFormat="1" ht="81" customHeight="1">
-      <c r="A38" s="86" t="s">
-        <v>103</v>
-      </c>
-      <c r="B38" s="86"/>
-      <c r="C38" s="86"/>
-      <c r="D38" s="86"/>
-      <c r="E38" s="86"/>
-      <c r="F38" s="86"/>
-      <c r="G38" s="86"/>
-      <c r="H38" s="86"/>
-      <c r="I38" s="86"/>
-      <c r="J38" s="86"/>
-      <c r="K38" s="86"/>
-      <c r="L38" s="86"/>
-      <c r="M38" s="86"/>
-      <c r="N38" s="86"/>
-      <c r="O38" s="86"/>
-      <c r="P38" s="86"/>
-      <c r="Q38" s="86"/>
-      <c r="R38" s="86"/>
-      <c r="S38" s="86"/>
-      <c r="T38" s="86"/>
-      <c r="U38" s="86"/>
-      <c r="V38" s="86"/>
-      <c r="W38" s="86"/>
-      <c r="X38" s="86"/>
-      <c r="Y38" s="86"/>
-      <c r="Z38" s="86"/>
+      <c r="A38" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" s="41"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="41"/>
+      <c r="I38" s="41"/>
+      <c r="J38" s="41"/>
+      <c r="K38" s="41"/>
+      <c r="L38" s="41"/>
+      <c r="M38" s="41"/>
+      <c r="N38" s="41"/>
+      <c r="O38" s="41"/>
+      <c r="P38" s="41"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="41"/>
+      <c r="S38" s="41"/>
+      <c r="T38" s="41"/>
+      <c r="U38" s="41"/>
+      <c r="V38" s="41"/>
+      <c r="W38" s="41"/>
+      <c r="X38" s="41"/>
+      <c r="Y38" s="41"/>
+      <c r="Z38" s="41"/>
     </row>
     <row r="39" spans="1:26" s="1" customFormat="1" ht="5.4" customHeight="1">
-      <c r="A39" s="41"/>
-      <c r="B39" s="41"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="41"/>
-      <c r="I39" s="41"/>
-      <c r="J39" s="41"/>
-      <c r="K39" s="41"/>
-      <c r="L39" s="41"/>
-      <c r="M39" s="41"/>
-      <c r="N39" s="41"/>
-      <c r="O39" s="41"/>
-      <c r="P39" s="41"/>
-      <c r="Q39" s="41"/>
-      <c r="R39" s="41"/>
-      <c r="S39" s="41"/>
-      <c r="T39" s="41"/>
-      <c r="U39" s="41"/>
-      <c r="V39" s="41"/>
-      <c r="W39" s="41"/>
-      <c r="X39" s="41"/>
-      <c r="Y39" s="41"/>
-      <c r="Z39" s="41"/>
+      <c r="A39" s="97"/>
+      <c r="B39" s="97"/>
+      <c r="C39" s="97"/>
+      <c r="D39" s="97"/>
+      <c r="E39" s="97"/>
+      <c r="F39" s="97"/>
+      <c r="G39" s="97"/>
+      <c r="H39" s="97"/>
+      <c r="I39" s="97"/>
+      <c r="J39" s="97"/>
+      <c r="K39" s="97"/>
+      <c r="L39" s="97"/>
+      <c r="M39" s="97"/>
+      <c r="N39" s="97"/>
+      <c r="O39" s="97"/>
+      <c r="P39" s="97"/>
+      <c r="Q39" s="97"/>
+      <c r="R39" s="97"/>
+      <c r="S39" s="97"/>
+      <c r="T39" s="97"/>
+      <c r="U39" s="97"/>
+      <c r="V39" s="97"/>
+      <c r="W39" s="97"/>
+      <c r="X39" s="97"/>
+      <c r="Y39" s="97"/>
+      <c r="Z39" s="97"/>
     </row>
     <row r="40" spans="1:26" ht="54" customHeight="1">
-      <c r="A40" s="88" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="88"/>
-      <c r="C40" s="88"/>
-      <c r="D40" s="96"/>
-      <c r="E40" s="97"/>
+      <c r="A40" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="48"/>
+      <c r="C40" s="48"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="58"/>
       <c r="F40" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="G40" s="85"/>
-      <c r="H40" s="85"/>
-      <c r="I40" s="85"/>
-      <c r="J40" s="85"/>
-      <c r="K40" s="85"/>
-      <c r="L40" s="85"/>
+        <v>72</v>
+      </c>
+      <c r="G40" s="40"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="40"/>
+      <c r="J40" s="40"/>
+      <c r="K40" s="40"/>
+      <c r="L40" s="40"/>
       <c r="M40" s="9"/>
-      <c r="N40" s="70" t="s">
-        <v>40</v>
-      </c>
-      <c r="O40" s="70"/>
-      <c r="P40" s="70"/>
-      <c r="Q40" s="93"/>
-      <c r="R40" s="94"/>
-      <c r="S40" s="94"/>
-      <c r="T40" s="94"/>
-      <c r="U40" s="94"/>
-      <c r="V40" s="94"/>
-      <c r="W40" s="95"/>
-      <c r="X40" s="70" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y40" s="70"/>
+      <c r="N40" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="O40" s="49"/>
+      <c r="P40" s="49"/>
+      <c r="Q40" s="54"/>
+      <c r="R40" s="55"/>
+      <c r="S40" s="55"/>
+      <c r="T40" s="55"/>
+      <c r="U40" s="55"/>
+      <c r="V40" s="55"/>
+      <c r="W40" s="56"/>
+      <c r="X40" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y40" s="49"/>
       <c r="Z40" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="113">
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="O28:U28"/>
-    <mergeCell ref="Y28:Z28"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="O29:U29"/>
-    <mergeCell ref="Y29:Z29"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="O26:U26"/>
-    <mergeCell ref="Y26:Z26"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="O27:U27"/>
-    <mergeCell ref="Y27:Z27"/>
-    <mergeCell ref="O24:U24"/>
-    <mergeCell ref="Y24:Z24"/>
-    <mergeCell ref="O25:U25"/>
-    <mergeCell ref="Y25:Z25"/>
-    <mergeCell ref="N30:Z34"/>
-    <mergeCell ref="A39:Z39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="G40:L40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="Q40:W40"/>
-    <mergeCell ref="X40:Y40"/>
-    <mergeCell ref="A35:Z35"/>
-    <mergeCell ref="A36:Q37"/>
-    <mergeCell ref="R36:W36"/>
-    <mergeCell ref="R37:W37"/>
-    <mergeCell ref="A38:Z38"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="O16:U16"/>
-    <mergeCell ref="Y16:Z16"/>
-    <mergeCell ref="O17:U17"/>
-    <mergeCell ref="Y17:Z17"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="O23:U23"/>
-    <mergeCell ref="Y23:Z23"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="O20:U20"/>
-    <mergeCell ref="Y20:Z20"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O21:U21"/>
-    <mergeCell ref="Y21:Z21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="O22:U22"/>
-    <mergeCell ref="Y22:Z22"/>
-    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="K7:U7"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="Y9:Z9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="K10:M10"/>
+    <mergeCell ref="O10:U10"/>
+    <mergeCell ref="Y10:Z10"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="O8:U8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="O9:U9"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="O14:U14"/>
+    <mergeCell ref="Y14:Z14"/>
+    <mergeCell ref="Y19:Z19"/>
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="E1:X2"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="W4:Y4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:G4"/>
     <mergeCell ref="A5:Z5"/>
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="J6:J34"/>
@@ -8601,40 +8577,61 @@
     <mergeCell ref="Y18:Z18"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="O19:U19"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="E1:X2"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:S4"/>
-    <mergeCell ref="W4:Y4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="K7:U7"/>
-    <mergeCell ref="V7:X7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="Y9:Z9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="K10:M10"/>
-    <mergeCell ref="O10:U10"/>
-    <mergeCell ref="Y10:Z10"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="O8:U8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="O9:U9"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="O14:U14"/>
-    <mergeCell ref="Y14:Z14"/>
-    <mergeCell ref="Y19:Z19"/>
+    <mergeCell ref="O16:U16"/>
+    <mergeCell ref="Y16:Z16"/>
+    <mergeCell ref="O17:U17"/>
+    <mergeCell ref="Y17:Z17"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="O23:U23"/>
+    <mergeCell ref="Y23:Z23"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="O20:U20"/>
+    <mergeCell ref="Y20:Z20"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O21:U21"/>
+    <mergeCell ref="Y21:Z21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="O22:U22"/>
+    <mergeCell ref="Y22:Z22"/>
+    <mergeCell ref="V16:X16"/>
+    <mergeCell ref="N30:Z34"/>
+    <mergeCell ref="A39:Z39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="G40:L40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="Q40:W40"/>
+    <mergeCell ref="X40:Y40"/>
+    <mergeCell ref="A35:Z35"/>
+    <mergeCell ref="A36:Q37"/>
+    <mergeCell ref="R36:W36"/>
+    <mergeCell ref="R37:W37"/>
+    <mergeCell ref="A38:Z38"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="O28:U28"/>
+    <mergeCell ref="Y28:Z28"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="O29:U29"/>
+    <mergeCell ref="Y29:Z29"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="O26:U26"/>
+    <mergeCell ref="Y26:Z26"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="O27:U27"/>
+    <mergeCell ref="Y27:Z27"/>
+    <mergeCell ref="O24:U24"/>
+    <mergeCell ref="Y24:Z24"/>
+    <mergeCell ref="O25:U25"/>
+    <mergeCell ref="Y25:Z25"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
